--- a/input_data/admin_data/COL/_clean/total-pos-COL-adults.xlsx
+++ b/input_data/admin_data/COL/_clean/total-pos-COL-adults.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1816" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="2129" uniqueCount="11">
   <si>
     <t>poptot</t>
   </si>
@@ -139,22 +139,22 @@
         <v>30643644</v>
       </c>
       <c r="B2" s="2">
-        <v>12202056</v>
+        <v>10637657</v>
       </c>
       <c r="C2" s="2">
-        <v>106382565048320</v>
+        <v>64189833936896</v>
       </c>
       <c r="D2" s="1">
-        <v>0.95003575086593628</v>
+        <v>0.95002275705337524</v>
       </c>
       <c r="E2" s="2">
-        <v>28339526</v>
+        <v>25055834</v>
       </c>
       <c r="F2" s="1">
-        <v>5329430.5</v>
+        <v>3219838</v>
       </c>
       <c r="G2" s="1">
-        <v>0.0022275620140135288</v>
+        <v>0.0027409023605287075</v>
       </c>
       <c r="H2" s="1">
         <v>2014</v>
@@ -168,22 +168,22 @@
         <v>30643644</v>
       </c>
       <c r="B3" s="2">
-        <v>39503000</v>
+        <v>33518326</v>
       </c>
       <c r="C3" s="2">
-        <v>125853329522688</v>
+        <v>73986599813120</v>
       </c>
       <c r="D3" s="1">
-        <v>0.96001219749450684</v>
+        <v>0.96002906560897827</v>
       </c>
       <c r="E3" s="2">
-        <v>47076976</v>
+        <v>38382776</v>
       </c>
       <c r="F3" s="1">
-        <v>5329430.5</v>
+        <v>3219838</v>
       </c>
       <c r="G3" s="1">
-        <v>0.0048309573903679848</v>
+        <v>0.0059095057658851147</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" t="s">
@@ -195,22 +195,22 @@
         <v>30643644</v>
       </c>
       <c r="B4" s="2">
-        <v>55761972</v>
+        <v>43388444</v>
       </c>
       <c r="C4" s="2">
-        <v>152267093180416</v>
+        <v>85864885518336</v>
       </c>
       <c r="D4" s="1">
-        <v>0.97005331516265869</v>
+        <v>0.9700283408164978</v>
       </c>
       <c r="E4" s="2">
-        <v>67378360</v>
+        <v>48879984</v>
       </c>
       <c r="F4" s="1">
-        <v>5329430.5</v>
+        <v>3219838</v>
       </c>
       <c r="G4" s="1">
-        <v>0.010106450878083706</v>
+        <v>0.014093345031142235</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" t="s">
@@ -222,22 +222,22 @@
         <v>30643644</v>
       </c>
       <c r="B5" s="2">
-        <v>81467624</v>
+        <v>54904500</v>
       </c>
       <c r="C5" s="2">
-        <v>194711100850176</v>
+        <v>104441281773568</v>
       </c>
       <c r="D5" s="1">
-        <v>0.98003548383712769</v>
+        <v>0.98004907369613647</v>
       </c>
       <c r="E5" s="2">
-        <v>101434392</v>
+        <v>64151816</v>
       </c>
       <c r="F5" s="1">
-        <v>5329430.5</v>
+        <v>3219838</v>
       </c>
       <c r="G5" s="1">
-        <v>0.017856409773230553</v>
+        <v>0.028034549206495285</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" t="s">
@@ -249,22 +249,22 @@
         <v>30643644</v>
       </c>
       <c r="B6" s="2">
-        <v>129192992</v>
+        <v>83531560</v>
       </c>
       <c r="C6" s="2">
-        <v>287988730822656</v>
+        <v>144666863337472</v>
       </c>
       <c r="D6" s="1">
-        <v>0.99001777172088623</v>
+        <v>0.9900166392326355</v>
       </c>
       <c r="E6" s="2">
-        <v>133395312</v>
+        <v>85426152</v>
       </c>
       <c r="F6" s="1">
-        <v>5329430.5</v>
+        <v>3219838</v>
       </c>
       <c r="G6" s="1">
-        <v>0.032092999666929245</v>
+        <v>0.04850386455655098</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" t="s">
@@ -276,22 +276,22 @@
         <v>30643644</v>
       </c>
       <c r="B7" s="2">
-        <v>137745392</v>
+        <v>88078264</v>
       </c>
       <c r="C7" s="2">
-        <v>305364356562944</v>
+        <v>151337803186176</v>
       </c>
       <c r="D7" s="1">
-        <v>0.99102640151977539</v>
+        <v>0.99102705717086792</v>
       </c>
       <c r="E7" s="2">
-        <v>142951248</v>
+        <v>91337232</v>
       </c>
       <c r="F7" s="1">
-        <v>5329430.5</v>
+        <v>3219838</v>
       </c>
       <c r="G7" s="1">
-        <v>0.0354728102684021</v>
+        <v>0.054049856960773468</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" t="s">
@@ -303,22 +303,22 @@
         <v>30643644</v>
       </c>
       <c r="B8" s="2">
-        <v>148585344</v>
+        <v>93819912</v>
       </c>
       <c r="C8" s="2">
-        <v>325940169146368</v>
+        <v>158931758350336</v>
       </c>
       <c r="D8" s="1">
-        <v>0.9920353889465332</v>
+        <v>0.99203509092330933</v>
       </c>
       <c r="E8" s="2">
-        <v>154586368</v>
+        <v>96209368</v>
       </c>
       <c r="F8" s="1">
-        <v>5329430.5</v>
+        <v>3219838</v>
       </c>
       <c r="G8" s="1">
-        <v>0.037771545350551605</v>
+        <v>0.05893336609005928</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" t="s">
@@ -330,22 +330,22 @@
         <v>30643644</v>
       </c>
       <c r="B9" s="2">
-        <v>161371520</v>
+        <v>99384424</v>
       </c>
       <c r="C9" s="2">
-        <v>350792292761600</v>
+        <v>168032307511296</v>
       </c>
       <c r="D9" s="1">
-        <v>0.99304425716400146</v>
+        <v>0.99304431676864624</v>
       </c>
       <c r="E9" s="2">
-        <v>169129936</v>
+        <v>102536640</v>
       </c>
       <c r="F9" s="1">
-        <v>5329430.5</v>
+        <v>3219838</v>
       </c>
       <c r="G9" s="1">
-        <v>0.039839901030063629</v>
+        <v>0.063126973807811737</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" t="s">
@@ -357,22 +357,22 @@
         <v>30643644</v>
       </c>
       <c r="B10" s="2">
-        <v>178658800</v>
+        <v>105589616</v>
       </c>
       <c r="C10" s="2">
-        <v>381612474761216</v>
+        <v>178464262979584</v>
       </c>
       <c r="D10" s="1">
-        <v>0.99405312538146973</v>
+        <v>0.99400001764297485</v>
       </c>
       <c r="E10" s="2">
-        <v>186761504</v>
+        <v>109544888</v>
       </c>
       <c r="F10" s="1">
-        <v>5329430.5</v>
+        <v>3219838</v>
       </c>
       <c r="G10" s="1">
-        <v>0.041206996887922287</v>
+        <v>0.068544134497642517</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" t="s">
@@ -384,22 +384,22 @@
         <v>30643644</v>
       </c>
       <c r="B11" s="2">
-        <v>197025184</v>
+        <v>114850760</v>
       </c>
       <c r="C11" s="2">
-        <v>418925170917376</v>
+        <v>192395928928256</v>
       </c>
       <c r="D11" s="1">
         <v>0.99500894546508789</v>
       </c>
       <c r="E11" s="2">
-        <v>209501376</v>
+        <v>120139640</v>
       </c>
       <c r="F11" s="1">
-        <v>5329430.5</v>
+        <v>3219838</v>
       </c>
       <c r="G11" s="1">
-        <v>0.044064141809940338</v>
+        <v>0.074533939361572266</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" t="s">
@@ -411,22 +411,22 @@
         <v>30643644</v>
       </c>
       <c r="B12" s="2">
-        <v>224964144</v>
+        <v>125736664</v>
       </c>
       <c r="C12" s="2">
-        <v>471978351788032</v>
+        <v>210699804475392</v>
       </c>
       <c r="D12" s="1">
-        <v>0.99601775407791138</v>
+        <v>0.9960176944732666</v>
       </c>
       <c r="E12" s="2">
-        <v>242546272</v>
+        <v>132766768</v>
       </c>
       <c r="F12" s="1">
-        <v>5329430.5</v>
+        <v>3219838</v>
       </c>
       <c r="G12" s="1">
-        <v>0.047493357211351395</v>
+        <v>0.083002790808677673</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" t="s">
@@ -438,22 +438,22 @@
         <v>30643644</v>
       </c>
       <c r="B13" s="2">
-        <v>264300960</v>
+        <v>142310624</v>
       </c>
       <c r="C13" s="2">
-        <v>549822989860864</v>
+        <v>237142760488960</v>
       </c>
       <c r="D13" s="1">
         <v>0.99702662229537964</v>
       </c>
       <c r="E13" s="2">
-        <v>292385856</v>
+        <v>150224752</v>
       </c>
       <c r="F13" s="1">
-        <v>5329430.5</v>
+        <v>3219838</v>
       </c>
       <c r="G13" s="1">
-        <v>0.049107853323221207</v>
+        <v>0.091954521834850311</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" t="s">
@@ -465,22 +465,22 @@
         <v>30643644</v>
       </c>
       <c r="B14" s="2">
-        <v>330274720</v>
+        <v>161393024</v>
       </c>
       <c r="C14" s="2">
-        <v>682018123808768</v>
+        <v>281779919388672</v>
       </c>
       <c r="D14" s="1">
-        <v>0.99803543090820313</v>
+        <v>0.9980354905128479</v>
       </c>
       <c r="E14" s="2">
-        <v>387736896</v>
+        <v>173777024</v>
       </c>
       <c r="F14" s="1">
-        <v>5329430.5</v>
+        <v>3219838</v>
       </c>
       <c r="G14" s="1">
-        <v>0.050105992704629898</v>
+        <v>0.1029641255736351</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" t="s">
@@ -492,22 +492,22 @@
         <v>30643644</v>
       </c>
       <c r="B15" s="2">
-        <v>478281344</v>
+        <v>195889648</v>
       </c>
       <c r="C15" s="2">
-        <v>992657807507456</v>
+        <v>395779122397184</v>
       </c>
       <c r="D15" s="1">
         <v>0.99904429912567139</v>
       </c>
       <c r="E15" s="2">
-        <v>484044832</v>
+        <v>220921984</v>
       </c>
       <c r="F15" s="1">
-        <v>5329430.5</v>
+        <v>3219838</v>
       </c>
       <c r="G15" s="1">
-        <v>0.052534863352775574</v>
+        <v>0.11666455119848251</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" t="s">
@@ -519,22 +519,22 @@
         <v>30643644</v>
       </c>
       <c r="B16" s="2">
-        <v>513076768</v>
+        <v>244455872</v>
       </c>
       <c r="C16" s="2">
-        <v>1094376189067264</v>
+        <v>430749148774400</v>
       </c>
       <c r="D16" s="1">
         <v>0.99920356273651123</v>
       </c>
       <c r="E16" s="2">
-        <v>524390752</v>
+        <v>248329344</v>
       </c>
       <c r="F16" s="1">
-        <v>5329430.5</v>
+        <v>3219838</v>
       </c>
       <c r="G16" s="1">
-        <v>0.059790723025798798</v>
+        <v>0.11835610866546631</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" t="s">
@@ -546,22 +546,22 @@
         <v>30643644</v>
       </c>
       <c r="B17" s="2">
-        <v>555739136</v>
+        <v>258503696</v>
       </c>
       <c r="C17" s="2">
-        <v>1182062107164672</v>
+        <v>458812397977600</v>
       </c>
       <c r="D17" s="1">
         <v>0.9993097186088562</v>
       </c>
       <c r="E17" s="2">
-        <v>569625600</v>
+        <v>259342224</v>
       </c>
       <c r="F17" s="1">
-        <v>5329430.5</v>
+        <v>3219838</v>
       </c>
       <c r="G17" s="1">
-        <v>0.060086462646722794</v>
+        <v>0.12303254008293152</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" t="s">
@@ -573,22 +573,22 @@
         <v>30643644</v>
       </c>
       <c r="B18" s="2">
-        <v>612485952</v>
+        <v>266409248</v>
       </c>
       <c r="C18" s="2">
-        <v>1293448460107776</v>
+        <v>495090845876224</v>
       </c>
       <c r="D18" s="1">
         <v>0.99941593408584595</v>
       </c>
       <c r="E18" s="2">
-        <v>629103872</v>
+        <v>275942048</v>
       </c>
       <c r="F18" s="1">
-        <v>5329430.5</v>
+        <v>3219838</v>
       </c>
       <c r="G18" s="1">
-        <v>0.057635478675365448</v>
+        <v>0.12332677841186523</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" t="s">
@@ -600,22 +600,22 @@
         <v>30643644</v>
       </c>
       <c r="B19" s="2">
-        <v>686542272</v>
+        <v>287425344</v>
       </c>
       <c r="C19" s="2">
-        <v>1441080578932736</v>
+        <v>543790607630336</v>
       </c>
       <c r="D19" s="1">
         <v>0.99952214956283569</v>
       </c>
       <c r="E19" s="2">
-        <v>709826560</v>
+        <v>289879584</v>
       </c>
       <c r="F19" s="1">
-        <v>5329430.5</v>
+        <v>3219838</v>
       </c>
       <c r="G19" s="1">
-        <v>0.054105959832668305</v>
+        <v>0.12183916568756104</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" t="s">
@@ -627,22 +627,22 @@
         <v>30643644</v>
       </c>
       <c r="B20" s="2">
-        <v>783016192</v>
+        <v>319392768</v>
       </c>
       <c r="C20" s="2">
-        <v>1650010202570752</v>
+        <v>616336598237184</v>
       </c>
       <c r="D20" s="1">
         <v>0.99962836503982544</v>
       </c>
       <c r="E20" s="2">
-        <v>818670400</v>
+        <v>328338016</v>
       </c>
       <c r="F20" s="1">
-        <v>5329430.5</v>
+        <v>3219838</v>
       </c>
       <c r="G20" s="1">
-        <v>0.05522579699754715</v>
+        <v>0.12712568044662476</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" t="s">
@@ -654,22 +654,22 @@
         <v>30643644</v>
       </c>
       <c r="B21" s="2">
-        <v>945913920</v>
+        <v>376759648</v>
       </c>
       <c r="C21" s="2">
-        <v>1982546166415360</v>
+        <v>731536009723904</v>
       </c>
       <c r="D21" s="1">
         <v>0.99973452091217041</v>
       </c>
       <c r="E21" s="2">
-        <v>1016148224</v>
+        <v>407412064</v>
       </c>
       <c r="F21" s="1">
-        <v>5329430.5</v>
+        <v>3219838</v>
       </c>
       <c r="G21" s="1">
-        <v>0.053384914994239807</v>
+        <v>0.12336988747119904</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" t="s">
@@ -681,22 +681,22 @@
         <v>30643644</v>
       </c>
       <c r="B22" s="2">
-        <v>1303722240</v>
+        <v>512199840</v>
       </c>
       <c r="C22" s="2">
-        <v>2626811661910016</v>
+        <v>947618632957952</v>
       </c>
       <c r="D22" s="1">
         <v>0.99984073638916016</v>
       </c>
       <c r="E22" s="2">
-        <v>2626811648</v>
+        <v>947618624</v>
       </c>
       <c r="F22" s="1">
-        <v>5329430.5</v>
+        <v>3219838</v>
       </c>
       <c r="G22" s="1">
-        <v>0.042943686246871948</v>
+        <v>0.10602042824029922</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" t="s">
@@ -746,22 +746,22 @@
         <v>37511548</v>
       </c>
       <c r="B2" s="2">
-        <v>4662817.5</v>
+        <v>4295359.5</v>
       </c>
       <c r="C2" s="2">
-        <v>129267190988800</v>
+        <v>75704049860608</v>
       </c>
       <c r="D2" s="1">
         <v>0.84004455804824829</v>
       </c>
       <c r="E2" s="2">
-        <v>14251487</v>
+        <v>13319886</v>
       </c>
       <c r="F2" s="1">
-        <v>20681164</v>
+        <v>12112351</v>
       </c>
       <c r="G2" s="1">
-        <v>0.00034965723170898855</v>
+        <v>0.0003720447130035609</v>
       </c>
       <c r="H2" s="1">
         <v>2023</v>
@@ -775,22 +775,22 @@
         <v>37511548</v>
       </c>
       <c r="B3" s="2">
-        <v>21474410</v>
+        <v>20104934</v>
       </c>
       <c r="C3" s="2">
-        <v>136993853931520</v>
+        <v>79894973251584</v>
       </c>
       <c r="D3" s="1">
         <v>0.85011380910873413</v>
       </c>
       <c r="E3" s="2">
-        <v>27052636</v>
+        <v>25213920</v>
       </c>
       <c r="F3" s="1">
-        <v>20681164</v>
+        <v>12112351</v>
       </c>
       <c r="G3" s="1">
-        <v>1.7376507457811385e-05</v>
+        <v>1.8648846889846027e-05</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" t="s">
@@ -802,22 +802,22 @@
         <v>37511548</v>
       </c>
       <c r="B4" s="2">
-        <v>32337848</v>
+        <v>30011184</v>
       </c>
       <c r="C4" s="2">
-        <v>144772509466624</v>
+        <v>83763816038400</v>
       </c>
       <c r="D4" s="1">
         <v>0.86001795530319214</v>
       </c>
       <c r="E4" s="2">
-        <v>36717628</v>
+        <v>34083124</v>
       </c>
       <c r="F4" s="1">
-        <v>20681164</v>
+        <v>12112351</v>
       </c>
       <c r="G4" s="1">
-        <v>1.4008140169607941e-05</v>
+        <v>1.5418081602547318e-05</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" t="s">
@@ -829,22 +829,22 @@
         <v>37511548</v>
       </c>
       <c r="B5" s="2">
-        <v>41027652</v>
+        <v>38096592</v>
       </c>
       <c r="C5" s="2">
-        <v>153147309817856</v>
+        <v>87633967448064</v>
       </c>
       <c r="D5" s="1">
-        <v>0.87008684873580933</v>
+        <v>0.87013453245162964</v>
       </c>
       <c r="E5" s="2">
-        <v>44593696</v>
+        <v>41262988</v>
       </c>
       <c r="F5" s="1">
-        <v>20681164</v>
+        <v>12112351</v>
       </c>
       <c r="G5" s="1">
-        <v>9.9256300018168986e-05</v>
+        <v>0.00011882751277880743</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" t="s">
@@ -856,22 +856,22 @@
         <v>37511548</v>
       </c>
       <c r="B6" s="2">
-        <v>47996340</v>
+        <v>44083756</v>
       </c>
       <c r="C6" s="2">
-        <v>162232105172992</v>
+        <v>91456974880768</v>
       </c>
       <c r="D6" s="1">
-        <v>0.88011956214904785</v>
+        <v>0.88002568483352661</v>
       </c>
       <c r="E6" s="2">
-        <v>51352888</v>
+        <v>46703212</v>
       </c>
       <c r="F6" s="1">
-        <v>20681164</v>
+        <v>12112351</v>
       </c>
       <c r="G6" s="1">
-        <v>0.00066967139719054103</v>
+        <v>0.00074602977838367224</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" t="s">
@@ -883,22 +883,22 @@
         <v>37511548</v>
       </c>
       <c r="B7" s="2">
-        <v>54866532</v>
+        <v>49594412</v>
       </c>
       <c r="C7" s="2">
-        <v>172257951350784</v>
+        <v>95585898070016</v>
       </c>
       <c r="D7" s="1">
-        <v>0.89006048440933228</v>
+        <v>0.89015942811965942</v>
       </c>
       <c r="E7" s="2">
-        <v>58195832</v>
+        <v>51730056</v>
       </c>
       <c r="F7" s="1">
-        <v>20681164</v>
+        <v>12112351</v>
       </c>
       <c r="G7" s="1">
-        <v>0.00094287260435521603</v>
+        <v>0.0010507331462576985</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" t="s">
@@ -910,22 +910,22 @@
         <v>37511548</v>
       </c>
       <c r="B8" s="2">
-        <v>61268048</v>
+        <v>53593896</v>
       </c>
       <c r="C8" s="2">
-        <v>183757843726336</v>
+        <v>99972703846400</v>
       </c>
       <c r="D8" s="1">
-        <v>0.90012955665588379</v>
+        <v>0.90014749765396118</v>
       </c>
       <c r="E8" s="2">
-        <v>64194472</v>
+        <v>55864528</v>
       </c>
       <c r="F8" s="1">
-        <v>20681164</v>
+        <v>12112351</v>
       </c>
       <c r="G8" s="1">
-        <v>0.0012243612436577678</v>
+        <v>0.0014678905718028545</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" t="s">
@@ -937,22 +937,22 @@
         <v>37511548</v>
       </c>
       <c r="B9" s="2">
-        <v>67405408</v>
+        <v>58164196</v>
       </c>
       <c r="C9" s="2">
-        <v>196921398394880</v>
+        <v>104823064100864</v>
       </c>
       <c r="D9" s="1">
-        <v>0.91003447771072388</v>
+        <v>0.91003996133804321</v>
       </c>
       <c r="E9" s="2">
-        <v>70872992</v>
+        <v>60399520</v>
       </c>
       <c r="F9" s="1">
-        <v>20681164</v>
+        <v>12112351</v>
       </c>
       <c r="G9" s="1">
-        <v>0.0019093587761744857</v>
+        <v>0.002243521623313427</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" t="s">
@@ -964,22 +964,22 @@
         <v>37511548</v>
       </c>
       <c r="B10" s="2">
-        <v>74708560</v>
+        <v>62839528</v>
       </c>
       <c r="C10" s="2">
-        <v>212808314650624</v>
+        <v>110425177849856</v>
       </c>
       <c r="D10" s="1">
-        <v>0.92010438442230225</v>
+        <v>0.92011409997940063</v>
       </c>
       <c r="E10" s="2">
-        <v>78596424</v>
+        <v>65178688</v>
       </c>
       <c r="F10" s="1">
-        <v>20681164</v>
+        <v>12112351</v>
       </c>
       <c r="G10" s="1">
-        <v>0.0029802171047776937</v>
+        <v>0.0036081122234463692</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" t="s">
@@ -991,22 +991,22 @@
         <v>37511548</v>
       </c>
       <c r="B11" s="2">
-        <v>82895624</v>
+        <v>67594560</v>
       </c>
       <c r="C11" s="2">
-        <v>231800743919616</v>
+        <v>116821550170112</v>
       </c>
       <c r="D11" s="1">
-        <v>0.93000888824462891</v>
+        <v>0.93000859022140503</v>
       </c>
       <c r="E11" s="2">
-        <v>87635336</v>
+        <v>70940584</v>
       </c>
       <c r="F11" s="1">
-        <v>20681164</v>
+        <v>12112351</v>
       </c>
       <c r="G11" s="1">
-        <v>0.0049323155544698238</v>
+        <v>0.0062370779924094677</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" t="s">
@@ -1018,22 +1018,22 @@
         <v>37511548</v>
       </c>
       <c r="B12" s="2">
-        <v>92754328</v>
+        <v>73969040</v>
       </c>
       <c r="C12" s="2">
-        <v>256025835864064</v>
+        <v>124530446041088</v>
       </c>
       <c r="D12" s="1">
-        <v>0.94007796049118042</v>
+        <v>0.94007682800292969</v>
       </c>
       <c r="E12" s="2">
-        <v>98461128</v>
+        <v>77072136</v>
       </c>
       <c r="F12" s="1">
-        <v>20681164</v>
+        <v>12112351</v>
       </c>
       <c r="G12" s="1">
-        <v>0.008396591991186142</v>
+        <v>0.010629122145473957</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" t="s">
@@ -1045,22 +1045,22 @@
         <v>37511548</v>
       </c>
       <c r="B13" s="2">
-        <v>104967664</v>
+        <v>80972288</v>
       </c>
       <c r="C13" s="2">
-        <v>287852835373056</v>
+        <v>134118255886336</v>
       </c>
       <c r="D13" s="1">
-        <v>0.95014780759811401</v>
+        <v>0.95014822483062744</v>
       </c>
       <c r="E13" s="2">
-        <v>112935280</v>
+        <v>85624168</v>
       </c>
       <c r="F13" s="1">
-        <v>20681164</v>
+        <v>12112351</v>
       </c>
       <c r="G13" s="1">
-        <v>0.013120471499860287</v>
+        <v>0.017242187634110451</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" t="s">
@@ -1072,22 +1072,22 @@
         <v>37511548</v>
       </c>
       <c r="B14" s="2">
-        <v>122045344</v>
+        <v>89542272</v>
       </c>
       <c r="C14" s="2">
-        <v>331220999208960</v>
+        <v>146141077307392</v>
       </c>
       <c r="D14" s="1">
         <v>0.96005219221115112</v>
       </c>
       <c r="E14" s="2">
-        <v>132912784</v>
+        <v>94620640</v>
       </c>
       <c r="F14" s="1">
-        <v>20681164</v>
+        <v>12112351</v>
       </c>
       <c r="G14" s="1">
-        <v>0.016330795362591744</v>
+        <v>0.022818721830844879</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" t="s">
@@ -1099,22 +1099,22 @@
         <v>37511548</v>
       </c>
       <c r="B15" s="2">
-        <v>144862656</v>
+        <v>99201384</v>
       </c>
       <c r="C15" s="2">
-        <v>398054649757696</v>
+        <v>163505160323072</v>
       </c>
       <c r="D15" s="1">
-        <v>0.97012174129486084</v>
+        <v>0.97012203931808472</v>
       </c>
       <c r="E15" s="2">
-        <v>162063408</v>
+        <v>112255712</v>
       </c>
       <c r="F15" s="1">
-        <v>20681164</v>
+        <v>12112351</v>
       </c>
       <c r="G15" s="1">
-        <v>0.025105981156229973</v>
+        <v>0.035761240869760513</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" t="s">
@@ -1126,22 +1126,22 @@
         <v>37511548</v>
       </c>
       <c r="B16" s="2">
-        <v>184622768</v>
+        <v>123708744</v>
       </c>
       <c r="C16" s="2">
-        <v>515076066902016</v>
+        <v>188917257076736</v>
       </c>
       <c r="D16" s="1">
-        <v>0.98002618551254272</v>
+        <v>0.98002612590789795</v>
       </c>
       <c r="E16" s="2">
-        <v>224771600</v>
+        <v>139524784</v>
       </c>
       <c r="F16" s="1">
-        <v>20681164</v>
+        <v>12112351</v>
       </c>
       <c r="G16" s="1">
-        <v>0.043693892657756806</v>
+        <v>0.068679966032505036</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" t="s">
@@ -1153,22 +1153,22 @@
         <v>37511548</v>
       </c>
       <c r="B17" s="2">
-        <v>284789408</v>
+        <v>158680960</v>
       </c>
       <c r="C17" s="2">
-        <v>810217193340928</v>
+        <v>239133595271168</v>
       </c>
       <c r="D17" s="1">
-        <v>0.99009561538696289</v>
+        <v>0.99009567499160767</v>
       </c>
       <c r="E17" s="2">
-        <v>292370240</v>
+        <v>159644000</v>
       </c>
       <c r="F17" s="1">
-        <v>20681164</v>
+        <v>12112351</v>
       </c>
       <c r="G17" s="1">
-        <v>0.052504267543554306</v>
+        <v>0.091446399688720703</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" t="s">
@@ -1180,22 +1180,22 @@
         <v>37511548</v>
       </c>
       <c r="B18" s="2">
-        <v>304377248</v>
+        <v>161442496</v>
       </c>
       <c r="C18" s="2">
-        <v>867757675511808</v>
+        <v>247965608312832</v>
       </c>
       <c r="D18" s="1">
         <v>0.99108606576919556</v>
       </c>
       <c r="E18" s="2">
-        <v>313461696</v>
+        <v>163195152</v>
       </c>
       <c r="F18" s="1">
-        <v>20681164</v>
+        <v>12112351</v>
       </c>
       <c r="G18" s="1">
-        <v>0.052570827305316925</v>
+        <v>0.097511395812034607</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" t="s">
@@ -1207,22 +1207,22 @@
         <v>37511548</v>
       </c>
       <c r="B19" s="2">
-        <v>327722880</v>
+        <v>165969456</v>
       </c>
       <c r="C19" s="2">
-        <v>937043081297920</v>
+        <v>258561007419392</v>
       </c>
       <c r="D19" s="1">
-        <v>0.99207651615142822</v>
+        <v>0.99207645654678345</v>
       </c>
       <c r="E19" s="2">
-        <v>338928576</v>
+        <v>167412544</v>
       </c>
       <c r="F19" s="1">
-        <v>20681164</v>
+        <v>12112351</v>
       </c>
       <c r="G19" s="1">
-        <v>0.05350099503993988</v>
+        <v>0.1012779101729393</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" t="s">
@@ -1234,22 +1234,22 @@
         <v>37511548</v>
       </c>
       <c r="B20" s="2">
-        <v>356337760</v>
+        <v>169273056</v>
       </c>
       <c r="C20" s="2">
-        <v>1022485684289536</v>
+        <v>271582173855744</v>
       </c>
       <c r="D20" s="1">
         <v>0.99306690692901611</v>
       </c>
       <c r="E20" s="2">
-        <v>370571456</v>
+        <v>171486992</v>
       </c>
       <c r="F20" s="1">
-        <v>20681164</v>
+        <v>12112351</v>
       </c>
       <c r="G20" s="1">
-        <v>0.053109142929315567</v>
+        <v>0.11184561997652054</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" t="s">
@@ -1261,22 +1261,22 @@
         <v>37511548</v>
       </c>
       <c r="B21" s="2">
-        <v>390716448</v>
+        <v>175588832</v>
       </c>
       <c r="C21" s="2">
-        <v>1131141511774208</v>
+        <v>288265152233472</v>
       </c>
       <c r="D21" s="1">
         <v>0.99405735731124878</v>
       </c>
       <c r="E21" s="2">
-        <v>409748352</v>
+        <v>177258256</v>
       </c>
       <c r="F21" s="1">
-        <v>20681164</v>
+        <v>12112351</v>
       </c>
       <c r="G21" s="1">
-        <v>0.054989688098430634</v>
+        <v>0.11467895656824112</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" t="s">
@@ -1288,22 +1288,22 @@
         <v>37511548</v>
       </c>
       <c r="B22" s="2">
-        <v>438109888</v>
+        <v>180527376</v>
       </c>
       <c r="C22" s="2">
-        <v>1275420737536000</v>
+        <v>310500265033728</v>
       </c>
       <c r="D22" s="1">
-        <v>0.99504780769348145</v>
+        <v>0.99504905939102173</v>
       </c>
       <c r="E22" s="2">
-        <v>461153664</v>
+        <v>187822640</v>
       </c>
       <c r="F22" s="1">
-        <v>20681164</v>
+        <v>12112351</v>
       </c>
       <c r="G22" s="1">
-        <v>0.052925065159797669</v>
+        <v>0.12136492878198624</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" t="s">
@@ -1315,22 +1315,22 @@
         <v>37511548</v>
       </c>
       <c r="B23" s="2">
-        <v>493741536</v>
+        <v>216335296</v>
       </c>
       <c r="C23" s="2">
-        <v>1478982188924928</v>
+        <v>341132911312896</v>
       </c>
       <c r="D23" s="1">
         <v>0.99603825807571411</v>
       </c>
       <c r="E23" s="2">
-        <v>533033280</v>
+        <v>221711216</v>
       </c>
       <c r="F23" s="1">
-        <v>20681164</v>
+        <v>12112351</v>
       </c>
       <c r="G23" s="1">
-        <v>0.060783930122852326</v>
+        <v>0.13418465852737427</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" t="s">
@@ -1342,22 +1342,22 @@
         <v>37511548</v>
       </c>
       <c r="B24" s="2">
-        <v>598899264</v>
+        <v>229675616</v>
       </c>
       <c r="C24" s="2">
-        <v>1794298555138048</v>
+        <v>380937997123584</v>
       </c>
       <c r="D24" s="1">
         <v>0.997028648853302</v>
       </c>
       <c r="E24" s="2">
-        <v>672344192</v>
+        <v>234085184</v>
       </c>
       <c r="F24" s="1">
-        <v>20681164</v>
+        <v>12112351</v>
       </c>
       <c r="G24" s="1">
-        <v>0.057759139686822891</v>
+        <v>0.14923371374607086</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" t="s">
@@ -1369,22 +1369,22 @@
         <v>37511548</v>
       </c>
       <c r="B25" s="2">
-        <v>803442880</v>
+        <v>239610704</v>
       </c>
       <c r="C25" s="2">
-        <v>2355298324971520</v>
+        <v>454367375261696</v>
       </c>
       <c r="D25" s="1">
         <v>0.99801915884017944</v>
       </c>
       <c r="E25" s="2">
-        <v>975232192</v>
+        <v>259023200</v>
       </c>
       <c r="F25" s="1">
-        <v>20681164</v>
+        <v>12112351</v>
       </c>
       <c r="G25" s="1">
-        <v>0.048307400196790695</v>
+        <v>0.15926802158355713</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" t="s">
@@ -1396,22 +1396,22 @@
         <v>37511548</v>
       </c>
       <c r="B26" s="2">
-        <v>1347622016</v>
+        <v>303727392</v>
       </c>
       <c r="C26" s="2">
-        <v>3735401508372480</v>
+        <v>649716815626240</v>
       </c>
       <c r="D26" s="1">
         <v>0.99900960922241211</v>
       </c>
       <c r="E26" s="2">
-        <v>1453161600</v>
+        <v>311387648</v>
       </c>
       <c r="F26" s="1">
-        <v>20681164</v>
+        <v>12112351</v>
       </c>
       <c r="G26" s="1">
-        <v>0.04338005930185318</v>
+        <v>0.17424716055393219</v>
       </c>
       <c r="H26" s="1"/>
       <c r="I26" t="s">
@@ -1423,22 +1423,22 @@
         <v>37511548</v>
       </c>
       <c r="B27" s="2">
-        <v>1873328640</v>
+        <v>333805376</v>
       </c>
       <c r="C27" s="2">
-        <v>4876521437134848</v>
+        <v>818881350336512</v>
       </c>
       <c r="D27" s="1">
         <v>0.99933969974517822</v>
       </c>
       <c r="E27" s="2">
-        <v>2136921856</v>
+        <v>359168992</v>
       </c>
       <c r="F27" s="1">
-        <v>20681164</v>
+        <v>12112351</v>
       </c>
       <c r="G27" s="1">
-        <v>0.034828528761863708</v>
+        <v>0.17587555944919586</v>
       </c>
       <c r="H27" s="1"/>
       <c r="I27" t="s">
@@ -1450,22 +1450,22 @@
         <v>37511548</v>
       </c>
       <c r="B28" s="2">
-        <v>3486912256</v>
+        <v>481343968</v>
       </c>
       <c r="C28" s="2">
-        <v>7616121087721472</v>
+        <v>1278593644625920</v>
       </c>
       <c r="D28" s="1">
         <v>0.99966984987258911</v>
       </c>
       <c r="E28" s="2">
-        <v>7616121344</v>
+        <v>1278593792</v>
       </c>
       <c r="F28" s="1">
-        <v>20681164</v>
+        <v>12112351</v>
       </c>
       <c r="G28" s="1">
-        <v>0.023982319980859757</v>
+        <v>0.13831782341003418</v>
       </c>
       <c r="H28" s="1"/>
       <c r="I28" t="s">
@@ -1515,22 +1515,22 @@
         <v>31247746</v>
       </c>
       <c r="B2" s="2">
-        <v>31137330</v>
+        <v>29218760</v>
       </c>
       <c r="C2" s="2">
-        <v>117144377360384</v>
+        <v>72943367356416</v>
       </c>
       <c r="D2" s="1">
-        <v>0.9500313401222229</v>
+        <v>0.95004945993423462</v>
       </c>
       <c r="E2" s="2">
-        <v>40263592</v>
+        <v>34452696</v>
       </c>
       <c r="F2" s="1">
-        <v>6010027.5</v>
+        <v>3783325.25</v>
       </c>
       <c r="G2" s="1">
-        <v>0.0033773905597627163</v>
+        <v>0.0039453520439565182</v>
       </c>
       <c r="H2" s="1">
         <v>2015</v>
@@ -1544,22 +1544,22 @@
         <v>31247746</v>
       </c>
       <c r="B3" s="2">
-        <v>48021372</v>
+        <v>39137812</v>
       </c>
       <c r="C3" s="2">
-        <v>136401475600384</v>
+        <v>82574546305024</v>
       </c>
       <c r="D3" s="1">
-        <v>0.9600403904914856</v>
+        <v>0.96004664897918701</v>
       </c>
       <c r="E3" s="2">
-        <v>56772320</v>
+        <v>44174608</v>
       </c>
       <c r="F3" s="1">
-        <v>6010027.5</v>
+        <v>3783325.25</v>
       </c>
       <c r="G3" s="1">
-        <v>0.007331132423132658</v>
+        <v>0.0094528822228312492</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" t="s">
@@ -1571,22 +1571,22 @@
         <v>31247746</v>
       </c>
       <c r="B4" s="2">
-        <v>67022600</v>
+        <v>50187172</v>
       </c>
       <c r="C4" s="2">
-        <v>162997062336512</v>
+        <v>95407463989248</v>
       </c>
       <c r="D4" s="1">
-        <v>0.97004514932632446</v>
+        <v>0.9700542688369751</v>
       </c>
       <c r="E4" s="2">
-        <v>79391400</v>
+        <v>57542860</v>
       </c>
       <c r="F4" s="1">
-        <v>6010027.5</v>
+        <v>3783325.25</v>
       </c>
       <c r="G4" s="1">
-        <v>0.015425448305904865</v>
+        <v>0.021295404061675072</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" t="s">
@@ -1598,22 +1598,22 @@
         <v>31247746</v>
       </c>
       <c r="B5" s="2">
-        <v>92392944</v>
+        <v>64475412</v>
       </c>
       <c r="C5" s="2">
-        <v>204924348530688</v>
+        <v>114377998991360</v>
       </c>
       <c r="D5" s="1">
-        <v>0.98004990816116333</v>
+        <v>0.98004961013793945</v>
       </c>
       <c r="E5" s="2">
-        <v>109894312</v>
+        <v>74818128</v>
       </c>
       <c r="F5" s="1">
-        <v>6010027.5</v>
+        <v>3783325.25</v>
       </c>
       <c r="G5" s="1">
-        <v>0.026283815503120422</v>
+        <v>0.037994083017110825</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" t="s">
@@ -1625,22 +1625,22 @@
         <v>31247746</v>
       </c>
       <c r="B6" s="2">
-        <v>135626624</v>
+        <v>91131552</v>
       </c>
       <c r="C6" s="2">
-        <v>300525606141952</v>
+        <v>154182430490624</v>
       </c>
       <c r="D6" s="1">
-        <v>0.99005484580993652</v>
+        <v>0.99005556106567383</v>
       </c>
       <c r="E6" s="2">
-        <v>139520048</v>
+        <v>93009472</v>
       </c>
       <c r="F6" s="1">
-        <v>6010027.5</v>
+        <v>3783325.25</v>
       </c>
       <c r="G6" s="1">
-        <v>0.035859253257513046</v>
+        <v>0.052692737430334091</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" t="s">
@@ -1652,22 +1652,22 @@
         <v>31247746</v>
       </c>
       <c r="B7" s="2">
-        <v>144110560</v>
+        <v>94784920</v>
       </c>
       <c r="C7" s="2">
-        <v>317583404302336</v>
+        <v>160659593494528</v>
       </c>
       <c r="D7" s="1">
-        <v>0.99100756645202637</v>
+        <v>0.99100768566131592</v>
       </c>
       <c r="E7" s="2">
-        <v>149058752</v>
+        <v>96733280</v>
       </c>
       <c r="F7" s="1">
-        <v>6010027.5</v>
+        <v>3783325.25</v>
       </c>
       <c r="G7" s="1">
-        <v>0.037392299622297287</v>
+        <v>0.056952182203531265</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" t="s">
@@ -1679,22 +1679,22 @@
         <v>31247746</v>
       </c>
       <c r="B8" s="2">
-        <v>154806272</v>
+        <v>98865464</v>
       </c>
       <c r="C8" s="2">
-        <v>338965596995584</v>
+        <v>168807901429760</v>
       </c>
       <c r="D8" s="1">
-        <v>0.99202001094818115</v>
+        <v>0.99202430248260498</v>
       </c>
       <c r="E8" s="2">
-        <v>160835536</v>
+        <v>101046168</v>
       </c>
       <c r="F8" s="1">
-        <v>6010027.5</v>
+        <v>3783325.25</v>
       </c>
       <c r="G8" s="1">
-        <v>0.039710354059934616</v>
+        <v>0.060783129185438156</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" t="s">
@@ -1706,22 +1706,22 @@
         <v>31247746</v>
       </c>
       <c r="B9" s="2">
-        <v>168720560</v>
+        <v>104928016</v>
       </c>
       <c r="C9" s="2">
-        <v>364848042999808</v>
+        <v>178626951643136</v>
       </c>
       <c r="D9" s="1">
-        <v>0.99303239583969116</v>
+        <v>0.993033766746521</v>
       </c>
       <c r="E9" s="2">
-        <v>175745920</v>
+        <v>107270576</v>
       </c>
       <c r="F9" s="1">
-        <v>6010027.5</v>
+        <v>3783325.25</v>
       </c>
       <c r="G9" s="1">
-        <v>0.040648102760314942</v>
+        <v>0.065509751439094543</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" t="s">
@@ -1733,22 +1733,22 @@
         <v>31247746</v>
       </c>
       <c r="B10" s="2">
-        <v>184818976</v>
+        <v>109863408</v>
       </c>
       <c r="C10" s="2">
-        <v>396993423736832</v>
+        <v>190741947088896</v>
       </c>
       <c r="D10" s="1">
-        <v>0.99404478073120117</v>
+        <v>0.99404484033584595</v>
       </c>
       <c r="E10" s="2">
-        <v>194289232</v>
+        <v>114461784</v>
       </c>
       <c r="F10" s="1">
-        <v>6010027.5</v>
+        <v>3783325.25</v>
       </c>
       <c r="G10" s="1">
-        <v>0.043097231537103653</v>
+        <v>0.07084963470697403</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" t="s">
@@ -1760,22 +1760,22 @@
         <v>31247746</v>
       </c>
       <c r="B11" s="2">
-        <v>206881504</v>
+        <v>121003056</v>
       </c>
       <c r="C11" s="2">
-        <v>438512771923968</v>
+        <v>206365226172416</v>
       </c>
       <c r="D11" s="1">
         <v>0.99505716562271118</v>
       </c>
       <c r="E11" s="2">
-        <v>218226496</v>
+        <v>125639160</v>
       </c>
       <c r="F11" s="1">
-        <v>6010027.5</v>
+        <v>3783325.25</v>
       </c>
       <c r="G11" s="1">
-        <v>0.045526504516601563</v>
+        <v>0.076285228133201599</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" t="s">
@@ -1787,22 +1787,22 @@
         <v>31247746</v>
       </c>
       <c r="B12" s="2">
-        <v>233650176</v>
+        <v>130759472</v>
       </c>
       <c r="C12" s="2">
-        <v>491109948063744</v>
+        <v>225643992186880</v>
       </c>
       <c r="D12" s="1">
-        <v>0.99600988626480103</v>
+        <v>0.99601006507873535</v>
       </c>
       <c r="E12" s="2">
-        <v>251781696</v>
+        <v>138857280</v>
       </c>
       <c r="F12" s="1">
-        <v>6010027.5</v>
+        <v>3783325.25</v>
       </c>
       <c r="G12" s="1">
-        <v>0.048756819218397141</v>
+        <v>0.08493737131357193</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" t="s">
@@ -1814,22 +1814,22 @@
         <v>31247746</v>
       </c>
       <c r="B13" s="2">
-        <v>275314144</v>
+        <v>147779152</v>
       </c>
       <c r="C13" s="2">
-        <v>572492766773248</v>
+        <v>255152162340864</v>
       </c>
       <c r="D13" s="1">
-        <v>0.99702239036560059</v>
+        <v>0.99702244997024536</v>
       </c>
       <c r="E13" s="2">
-        <v>302962688</v>
+        <v>156803728</v>
       </c>
       <c r="F13" s="1">
-        <v>6010027.5</v>
+        <v>3783325.25</v>
       </c>
       <c r="G13" s="1">
-        <v>0.0507613904774189</v>
+        <v>0.093359202146530151</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" t="s">
@@ -1841,22 +1841,22 @@
         <v>31247746</v>
       </c>
       <c r="B14" s="2">
-        <v>343097088</v>
+        <v>170518608</v>
       </c>
       <c r="C14" s="2">
-        <v>711344160505856</v>
+        <v>305815831445504</v>
       </c>
       <c r="D14" s="1">
         <v>0.9980347752571106</v>
       </c>
       <c r="E14" s="2">
-        <v>406009568</v>
+        <v>183785072</v>
       </c>
       <c r="F14" s="1">
-        <v>6010027.5</v>
+        <v>3783325.25</v>
       </c>
       <c r="G14" s="1">
-        <v>0.051412466913461685</v>
+        <v>0.10710126906633377</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" t="s">
@@ -1868,22 +1868,22 @@
         <v>31247746</v>
       </c>
       <c r="B15" s="2">
-        <v>501217952</v>
+        <v>245476528</v>
       </c>
       <c r="C15" s="2">
-        <v>1077739163484160</v>
+        <v>452250090602496</v>
       </c>
       <c r="D15" s="1">
         <v>0.99910670518875122</v>
       </c>
       <c r="E15" s="2">
-        <v>512212960</v>
+        <v>246756864</v>
       </c>
       <c r="F15" s="1">
-        <v>6010027.5</v>
+        <v>3783325.25</v>
       </c>
       <c r="G15" s="1">
-        <v>0.062231332063674927</v>
+        <v>0.12102578580379486</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" t="s">
@@ -1895,22 +1895,22 @@
         <v>31247746</v>
       </c>
       <c r="B16" s="2">
-        <v>545959744</v>
+        <v>260494896</v>
       </c>
       <c r="C16" s="2">
-        <v>1164750301954048</v>
+        <v>483867056144384</v>
       </c>
       <c r="D16" s="1">
         <v>0.99922585487365723</v>
       </c>
       <c r="E16" s="2">
-        <v>571285056</v>
+        <v>265152768</v>
       </c>
       <c r="F16" s="1">
-        <v>6010027.5</v>
+        <v>3783325.25</v>
       </c>
       <c r="G16" s="1">
-        <v>0.060031738132238388</v>
+        <v>0.1208764985203743</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" t="s">
@@ -1922,22 +1922,22 @@
         <v>31247746</v>
       </c>
       <c r="B17" s="2">
-        <v>628331456</v>
+        <v>291183552</v>
       </c>
       <c r="C17" s="2">
-        <v>1342809042845696</v>
+        <v>549488385064960</v>
       </c>
       <c r="D17" s="1">
         <v>0.99940448999404907</v>
       </c>
       <c r="E17" s="2">
-        <v>647808576</v>
+        <v>294812128</v>
       </c>
       <c r="F17" s="1">
-        <v>6010027.5</v>
+        <v>3783325.25</v>
       </c>
       <c r="G17" s="1">
-        <v>0.062790066003799438</v>
+        <v>0.12827104330062866</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" t="s">
@@ -1949,22 +1949,22 @@
         <v>31247746</v>
       </c>
       <c r="B18" s="2">
-        <v>717668544</v>
+        <v>302491456</v>
       </c>
       <c r="C18" s="2">
-        <v>1516582480117760</v>
+        <v>613166039957504</v>
       </c>
       <c r="D18" s="1">
         <v>0.99952363967895508</v>
       </c>
       <c r="E18" s="2">
-        <v>778158080</v>
+        <v>318391328</v>
       </c>
       <c r="F18" s="1">
-        <v>6010027.5</v>
+        <v>3783325.25</v>
       </c>
       <c r="G18" s="1">
-        <v>0.056957736611366272</v>
+        <v>0.12846976518630981</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" t="s">
@@ -1976,22 +1976,22 @@
         <v>31247746</v>
       </c>
       <c r="B19" s="2">
-        <v>941614208</v>
+        <v>383243808</v>
       </c>
       <c r="C19" s="2">
-        <v>1959605538127872</v>
+        <v>790018096365568</v>
       </c>
       <c r="D19" s="1">
         <v>0.99970227479934692</v>
       </c>
       <c r="E19" s="2">
-        <v>1009495232</v>
+        <v>404239904</v>
       </c>
       <c r="F19" s="1">
-        <v>6010027.5</v>
+        <v>3783325.25</v>
       </c>
       <c r="G19" s="1">
-        <v>0.059331931173801422</v>
+        <v>0.13601958751678467</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" t="s">
@@ -2003,22 +2003,22 @@
         <v>31247746</v>
       </c>
       <c r="B20" s="2">
-        <v>1311043200</v>
+        <v>522488896</v>
       </c>
       <c r="C20" s="2">
-        <v>2593125964972032</v>
+        <v>1047249660411904</v>
       </c>
       <c r="D20" s="1">
         <v>0.99982136487960816</v>
       </c>
       <c r="E20" s="2">
-        <v>2593125632</v>
+        <v>1047249664</v>
       </c>
       <c r="F20" s="1">
-        <v>6010027.5</v>
+        <v>3783325.25</v>
       </c>
       <c r="G20" s="1">
-        <v>0.047024995088577271</v>
+        <v>0.10973061621189117</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" t="s">
@@ -2068,22 +2068,22 @@
         <v>31890754</v>
       </c>
       <c r="B2" s="2">
-        <v>10799593</v>
+        <v>9240560</v>
       </c>
       <c r="C2" s="2">
-        <v>108416190119936</v>
+        <v>69603753459712</v>
       </c>
       <c r="D2" s="1">
-        <v>0.94003432989120483</v>
+        <v>0.94003033638000488</v>
       </c>
       <c r="E2" s="2">
-        <v>26199530</v>
+        <v>23141734</v>
       </c>
       <c r="F2" s="1">
-        <v>6514638</v>
+        <v>4184905.5</v>
       </c>
       <c r="G2" s="1">
-        <v>0.0021987073123455048</v>
+        <v>0.0029344626236706972</v>
       </c>
       <c r="H2" s="1">
         <v>2016</v>
@@ -2097,22 +2097,22 @@
         <v>31890754</v>
       </c>
       <c r="B3" s="2">
-        <v>38180364</v>
+        <v>32396718</v>
       </c>
       <c r="C3" s="2">
-        <v>124832897302528</v>
+        <v>78924386140160</v>
       </c>
       <c r="D3" s="1">
-        <v>0.950015127658844</v>
+        <v>0.95005059242248535</v>
       </c>
       <c r="E3" s="2">
-        <v>45863864</v>
+        <v>38199560</v>
       </c>
       <c r="F3" s="1">
-        <v>6514638</v>
+        <v>4184905.5</v>
       </c>
       <c r="G3" s="1">
-        <v>0.0035285218618810177</v>
+        <v>0.0043390830978751183</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" t="s">
@@ -2124,22 +2124,22 @@
         <v>31890754</v>
       </c>
       <c r="B4" s="2">
-        <v>53002416</v>
+        <v>42428940</v>
       </c>
       <c r="C4" s="2">
-        <v>144669195370496</v>
+        <v>89115504672768</v>
       </c>
       <c r="D4" s="1">
-        <v>0.96005016565322876</v>
+        <v>0.96004825830459595</v>
       </c>
       <c r="E4" s="2">
-        <v>62049992</v>
+        <v>47669560</v>
       </c>
       <c r="F4" s="1">
-        <v>6514638</v>
+        <v>4184905.5</v>
       </c>
       <c r="G4" s="1">
-        <v>0.0075881709344685078</v>
+        <v>0.010587168857455254</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" t="s">
@@ -2151,22 +2151,22 @@
         <v>31890754</v>
       </c>
       <c r="B5" s="2">
-        <v>72538120</v>
+        <v>53699844</v>
       </c>
       <c r="C5" s="2">
-        <v>172150895935488</v>
+        <v>102924805996544</v>
       </c>
       <c r="D5" s="1">
-        <v>0.97002178430557251</v>
+        <v>0.97003293037414551</v>
       </c>
       <c r="E5" s="2">
-        <v>84754664</v>
+        <v>60721708</v>
       </c>
       <c r="F5" s="1">
-        <v>6514638</v>
+        <v>4184905.5</v>
       </c>
       <c r="G5" s="1">
-        <v>0.015410643070936203</v>
+        <v>0.021152980625629425</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" t="s">
@@ -2178,22 +2178,22 @@
         <v>31890754</v>
       </c>
       <c r="B6" s="2">
-        <v>97717952</v>
+        <v>66400580</v>
       </c>
       <c r="C6" s="2">
-        <v>216123626749952</v>
+        <v>124150433710080</v>
       </c>
       <c r="D6" s="1">
-        <v>0.98005634546279907</v>
+        <v>0.98006099462509155</v>
       </c>
       <c r="E6" s="2">
-        <v>115884904</v>
+        <v>81085952</v>
       </c>
       <c r="F6" s="1">
-        <v>6514638</v>
+        <v>4184905.5</v>
       </c>
       <c r="G6" s="1">
-        <v>0.026116589084267616</v>
+        <v>0.036811958998441696</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" t="s">
@@ -2205,22 +2205,22 @@
         <v>31890754</v>
       </c>
       <c r="B7" s="2">
-        <v>143233328</v>
+        <v>97317272</v>
       </c>
       <c r="C7" s="2">
-        <v>316368968744960</v>
+        <v>167196365946880</v>
       </c>
       <c r="D7" s="1">
-        <v>0.9900285005569458</v>
+        <v>0.99002838134765625</v>
       </c>
       <c r="E7" s="2">
-        <v>147402672</v>
+        <v>98708080</v>
       </c>
       <c r="F7" s="1">
-        <v>6514638</v>
+        <v>4184905.5</v>
       </c>
       <c r="G7" s="1">
-        <v>0.035265985876321793</v>
+        <v>0.051487904042005539</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" t="s">
@@ -2232,22 +2232,22 @@
         <v>31890754</v>
       </c>
       <c r="B8" s="2">
-        <v>152610832</v>
+        <v>100761968</v>
       </c>
       <c r="C8" s="2">
-        <v>335540125696000</v>
+        <v>174979584884736</v>
       </c>
       <c r="D8" s="1">
-        <v>0.99104458093643188</v>
+        <v>0.99104595184326172</v>
       </c>
       <c r="E8" s="2">
-        <v>157541008</v>
+        <v>102638120</v>
       </c>
       <c r="F8" s="1">
-        <v>6514638</v>
+        <v>4184905.5</v>
       </c>
       <c r="G8" s="1">
-        <v>0.036791130900382996</v>
+        <v>0.054229471832513809</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" t="s">
@@ -2259,22 +2259,22 @@
         <v>31890754</v>
       </c>
       <c r="B9" s="2">
-        <v>163921712</v>
+        <v>105042528</v>
       </c>
       <c r="C9" s="2">
-        <v>358321672421376</v>
+        <v>184228310417408</v>
       </c>
       <c r="D9" s="1">
-        <v>0.99206072092056274</v>
+        <v>0.99206089973449707</v>
       </c>
       <c r="E9" s="2">
-        <v>169403200</v>
+        <v>107895248</v>
       </c>
       <c r="F9" s="1">
-        <v>6514638</v>
+        <v>4184905.5</v>
       </c>
       <c r="G9" s="1">
-        <v>0.038856104016304016</v>
+        <v>0.05960778146982193</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" t="s">
@@ -2286,22 +2286,22 @@
         <v>31890754</v>
       </c>
       <c r="B10" s="2">
-        <v>176448000</v>
+        <v>110404904</v>
       </c>
       <c r="C10" s="2">
-        <v>384088288526336</v>
+        <v>194650216333312</v>
       </c>
       <c r="D10" s="1">
-        <v>0.99301356077194214</v>
+        <v>0.9930146336555481</v>
       </c>
       <c r="E10" s="2">
-        <v>184185856</v>
+        <v>113612872</v>
       </c>
       <c r="F10" s="1">
-        <v>6514638</v>
+        <v>4184905.5</v>
       </c>
       <c r="G10" s="1">
-        <v>0.039642833173274994</v>
+        <v>0.062310691922903061</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" t="s">
@@ -2313,22 +2313,22 @@
         <v>31890754</v>
       </c>
       <c r="B11" s="2">
-        <v>193579888</v>
+        <v>116990440</v>
       </c>
       <c r="C11" s="2">
-        <v>418113522761728</v>
+        <v>208429075398656</v>
       </c>
       <c r="D11" s="1">
         <v>0.99402976036071777</v>
       </c>
       <c r="E11" s="2">
-        <v>203369328</v>
+        <v>122112264</v>
       </c>
       <c r="F11" s="1">
-        <v>6514638</v>
+        <v>4184905.5</v>
       </c>
       <c r="G11" s="1">
-        <v>0.042176220566034317</v>
+        <v>0.067593507468700409</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" t="s">
@@ -2340,22 +2340,22 @@
         <v>31890754</v>
       </c>
       <c r="B12" s="2">
-        <v>215660992</v>
+        <v>129846560</v>
       </c>
       <c r="C12" s="2">
-        <v>462165861466112</v>
+        <v>226135296180224</v>
       </c>
       <c r="D12" s="1">
         <v>0.99504601955413818</v>
       </c>
       <c r="E12" s="2">
-        <v>228738688</v>
+        <v>134331536</v>
       </c>
       <c r="F12" s="1">
-        <v>6514638</v>
+        <v>4184905.5</v>
       </c>
       <c r="G12" s="1">
-        <v>0.04556858167052269</v>
+        <v>0.075485080480575562</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" t="s">
@@ -2367,22 +2367,22 @@
         <v>31890754</v>
       </c>
       <c r="B13" s="2">
-        <v>245264752</v>
+        <v>140157760</v>
       </c>
       <c r="C13" s="2">
-        <v>522397174202368</v>
+        <v>249826050572288</v>
       </c>
       <c r="D13" s="1">
-        <v>0.99606209993362427</v>
+        <v>0.99606215953826904</v>
       </c>
       <c r="E13" s="2">
-        <v>263724848</v>
+        <v>146118496</v>
       </c>
       <c r="F13" s="1">
-        <v>6514638</v>
+        <v>4184905.5</v>
       </c>
       <c r="G13" s="1">
-        <v>0.04819105938076973</v>
+        <v>0.083559408783912659</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" t="s">
@@ -2394,22 +2394,22 @@
         <v>31890754</v>
       </c>
       <c r="B14" s="2">
-        <v>286713728</v>
+        <v>157181712</v>
       </c>
       <c r="C14" s="2">
-        <v>604960236503040</v>
+        <v>282925266370560</v>
       </c>
       <c r="D14" s="1">
         <v>0.99701488018035889</v>
       </c>
       <c r="E14" s="2">
-        <v>316379968</v>
+        <v>166980720</v>
       </c>
       <c r="F14" s="1">
-        <v>6514638</v>
+        <v>4184905.5</v>
       </c>
       <c r="G14" s="1">
-        <v>0.051128000020980835</v>
+        <v>0.092322118580341339</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" t="s">
@@ -2421,22 +2421,22 @@
         <v>31890754</v>
       </c>
       <c r="B15" s="2">
-        <v>357449312</v>
+        <v>176180176</v>
       </c>
       <c r="C15" s="2">
-        <v>753908561477632</v>
+        <v>342771843989504</v>
       </c>
       <c r="D15" s="1">
         <v>0.9980311393737793</v>
       </c>
       <c r="E15" s="2">
-        <v>423247360</v>
+        <v>196513280</v>
       </c>
       <c r="F15" s="1">
-        <v>6514638</v>
+        <v>4184905.5</v>
       </c>
       <c r="G15" s="1">
-        <v>0.051658809185028076</v>
+        <v>0.10505262762308121</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" t="s">
@@ -2448,22 +2448,22 @@
         <v>31890754</v>
       </c>
       <c r="B16" s="2">
-        <v>527300416</v>
+        <v>259300352</v>
       </c>
       <c r="C16" s="2">
-        <v>1155433981018112</v>
+        <v>520370083856384</v>
       </c>
       <c r="D16" s="1">
         <v>0.99911081790924072</v>
       </c>
       <c r="E16" s="2">
-        <v>551754688</v>
+        <v>268203376</v>
       </c>
       <c r="F16" s="1">
-        <v>6514638</v>
+        <v>4184905.5</v>
       </c>
       <c r="G16" s="1">
-        <v>0.06114998459815979</v>
+        <v>0.11813382804393768</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" t="s">
@@ -2475,22 +2475,22 @@
         <v>31890754</v>
       </c>
       <c r="B17" s="2">
-        <v>606838080</v>
+        <v>280450432</v>
       </c>
       <c r="C17" s="2">
-        <v>1320063835570176</v>
+        <v>589138717835264</v>
       </c>
       <c r="D17" s="1">
         <v>0.99930137395858765</v>
       </c>
       <c r="E17" s="2">
-        <v>624273856</v>
+        <v>282266048</v>
       </c>
       <c r="F17" s="1">
-        <v>6514638</v>
+        <v>4184905.5</v>
       </c>
       <c r="G17" s="1">
-        <v>0.058097310364246369</v>
+        <v>0.12000765651464462</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" t="s">
@@ -2502,22 +2502,22 @@
         <v>31890754</v>
       </c>
       <c r="B18" s="2">
-        <v>679037184</v>
+        <v>312723552</v>
       </c>
       <c r="C18" s="2">
-        <v>1474688161153024</v>
+        <v>657334544105472</v>
       </c>
       <c r="D18" s="1">
         <v>0.999428391456604</v>
       </c>
       <c r="E18" s="2">
-        <v>731992704</v>
+        <v>328281376</v>
       </c>
       <c r="F18" s="1">
-        <v>6514638</v>
+        <v>4184905.5</v>
       </c>
       <c r="G18" s="1">
-        <v>0.058944627642631531</v>
+        <v>0.12250236421823502</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" t="s">
@@ -2529,22 +2529,22 @@
         <v>31890754</v>
       </c>
       <c r="B19" s="2">
-        <v>858531456</v>
+        <v>374109888</v>
       </c>
       <c r="C19" s="2">
-        <v>1846096934469632</v>
+        <v>821888095879168</v>
       </c>
       <c r="D19" s="1">
         <v>0.99961894750595093</v>
       </c>
       <c r="E19" s="2">
-        <v>968796224</v>
+        <v>422930112</v>
       </c>
       <c r="F19" s="1">
-        <v>6514638</v>
+        <v>4184905.5</v>
       </c>
       <c r="G19" s="1">
-        <v>0.057281993329524994</v>
+        <v>0.12223166227340698</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" t="s">
@@ -2556,22 +2556,22 @@
         <v>31890754</v>
       </c>
       <c r="B20" s="2">
-        <v>1322199680</v>
+        <v>563610048</v>
       </c>
       <c r="C20" s="2">
-        <v>2723397691768832</v>
+        <v>1220846198718464</v>
       </c>
       <c r="D20" s="1">
         <v>0.99980950355529785</v>
       </c>
       <c r="E20" s="2">
-        <v>2723397632</v>
+        <v>1220846208</v>
       </c>
       <c r="F20" s="1">
-        <v>6514638</v>
+        <v>4184905.5</v>
       </c>
       <c r="G20" s="1">
-        <v>0.051203593611717224</v>
+        <v>0.10975739359855652</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" t="s">
@@ -2621,22 +2621,22 @@
         <v>32705576</v>
       </c>
       <c r="B2" s="2">
-        <v>9602872</v>
+        <v>8533323</v>
       </c>
       <c r="C2" s="2">
-        <v>129237344321536</v>
+        <v>66788347871232</v>
       </c>
       <c r="D2" s="1">
         <v>0.91001802682876587</v>
       </c>
       <c r="E2" s="2">
-        <v>20607192</v>
+        <v>18301462</v>
       </c>
       <c r="F2" s="1">
-        <v>11639880</v>
+        <v>6018884.5</v>
       </c>
       <c r="G2" s="1">
-        <v>0.0032582688145339489</v>
+        <v>0.0036774363834410906</v>
       </c>
       <c r="H2" s="1">
         <v>2017</v>
@@ -2650,22 +2650,22 @@
         <v>32705576</v>
       </c>
       <c r="B3" s="2">
-        <v>30447620</v>
+        <v>26139142</v>
       </c>
       <c r="C3" s="2">
-        <v>142832912302080</v>
+        <v>72891878080512</v>
       </c>
       <c r="D3" s="1">
-        <v>0.92002701759338379</v>
+        <v>0.92007851600646973</v>
       </c>
       <c r="E3" s="2">
-        <v>38593272</v>
+        <v>32980538</v>
       </c>
       <c r="F3" s="1">
-        <v>11639880</v>
+        <v>6018884.5</v>
       </c>
       <c r="G3" s="1">
-        <v>0.0034145996905863285</v>
+        <v>0.0040376759134232998</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" t="s">
@@ -2677,22 +2677,22 @@
         <v>32705576</v>
       </c>
       <c r="B4" s="2">
-        <v>45345652</v>
+        <v>38799668</v>
       </c>
       <c r="C4" s="2">
-        <v>157744216670208</v>
+        <v>78573129957376</v>
       </c>
       <c r="D4" s="1">
-        <v>0.93003535270690918</v>
+        <v>0.93003743886947632</v>
       </c>
       <c r="E4" s="2">
-        <v>49344048</v>
+        <v>43473288</v>
       </c>
       <c r="F4" s="1">
-        <v>11639880</v>
+        <v>6018884.5</v>
       </c>
       <c r="G4" s="1">
-        <v>0.0024333817418664694</v>
+        <v>0.002885730005800724</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" t="s">
@@ -2704,22 +2704,22 @@
         <v>32705576</v>
       </c>
       <c r="B5" s="2">
-        <v>53385564</v>
+        <v>47466292</v>
       </c>
       <c r="C5" s="2">
-        <v>175838276354048</v>
+        <v>84436951498752</v>
       </c>
       <c r="D5" s="1">
-        <v>0.94004327058792114</v>
+        <v>0.94005239009857178</v>
       </c>
       <c r="E5" s="2">
-        <v>57683772</v>
+        <v>50094716</v>
       </c>
       <c r="F5" s="1">
-        <v>11639880</v>
+        <v>6018884.5</v>
       </c>
       <c r="G5" s="1">
-        <v>0.0039467271417379379</v>
+        <v>0.004657277837395668</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" t="s">
@@ -2731,22 +2731,22 @@
         <v>32705576</v>
       </c>
       <c r="B6" s="2">
-        <v>62480740</v>
+        <v>53101976</v>
       </c>
       <c r="C6" s="2">
-        <v>199512756846592</v>
+        <v>91334677364736</v>
       </c>
       <c r="D6" s="1">
-        <v>0.95005136728286743</v>
+        <v>0.95007914304733276</v>
       </c>
       <c r="E6" s="2">
-        <v>68181408</v>
+        <v>56737820</v>
       </c>
       <c r="F6" s="1">
-        <v>11639880</v>
+        <v>6018884.5</v>
       </c>
       <c r="G6" s="1">
-        <v>0.0086646173149347305</v>
+        <v>0.010495714843273163</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" t="s">
@@ -2758,22 +2758,22 @@
         <v>32705576</v>
       </c>
       <c r="B7" s="2">
-        <v>74712448</v>
+        <v>60405236</v>
       </c>
       <c r="C7" s="2">
-        <v>232421786124288</v>
+        <v>100001745207296</v>
       </c>
       <c r="D7" s="1">
-        <v>0.96005964279174805</v>
+        <v>0.96007978916168213</v>
       </c>
       <c r="E7" s="2">
-        <v>82774968</v>
+        <v>64631820</v>
       </c>
       <c r="F7" s="1">
-        <v>11639880</v>
+        <v>6018884.5</v>
       </c>
       <c r="G7" s="1">
-        <v>0.014370170421898365</v>
+        <v>0.018766403198242188</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" t="s">
@@ -2785,22 +2785,22 @@
         <v>32705576</v>
       </c>
       <c r="B8" s="2">
-        <v>92127056</v>
+        <v>68008784</v>
       </c>
       <c r="C8" s="2">
-        <v>282442418094080</v>
+        <v>111831074996224</v>
       </c>
       <c r="D8" s="1">
-        <v>0.97006547451019287</v>
+        <v>0.9700847864151001</v>
       </c>
       <c r="E8" s="2">
-        <v>104668160</v>
+        <v>74160040</v>
       </c>
       <c r="F8" s="1">
-        <v>11639880</v>
+        <v>6018884.5</v>
       </c>
       <c r="G8" s="1">
-        <v>0.020542195066809654</v>
+        <v>0.028255237266421318</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" t="s">
@@ -2812,22 +2812,22 @@
         <v>32705576</v>
       </c>
       <c r="B9" s="2">
-        <v>120215168</v>
+        <v>86444592</v>
       </c>
       <c r="C9" s="2">
-        <v>371774550179840</v>
+        <v>130723872768000</v>
       </c>
       <c r="D9" s="1">
-        <v>0.98007690906524658</v>
+        <v>0.98007673025131226</v>
       </c>
       <c r="E9" s="2">
-        <v>149433936</v>
+        <v>98086960</v>
       </c>
       <c r="F9" s="1">
-        <v>11639880</v>
+        <v>6018884.5</v>
       </c>
       <c r="G9" s="1">
-        <v>0.033436398953199387</v>
+        <v>0.050058051943778992</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" t="s">
@@ -2839,22 +2839,22 @@
         <v>32705576</v>
       </c>
       <c r="B10" s="2">
-        <v>194244704</v>
+        <v>110491392</v>
       </c>
       <c r="C10" s="2">
-        <v>596211992100864</v>
+        <v>163669979693056</v>
       </c>
       <c r="D10" s="1">
-        <v>0.9900851845741272</v>
+        <v>0.99008530378341675</v>
       </c>
       <c r="E10" s="2">
-        <v>200781392</v>
+        <v>112482744</v>
       </c>
       <c r="F10" s="1">
-        <v>11639880</v>
+        <v>6018884.5</v>
       </c>
       <c r="G10" s="1">
-        <v>0.03779330849647522</v>
+        <v>0.064833708107471466</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" t="s">
@@ -2866,22 +2866,22 @@
         <v>32705576</v>
       </c>
       <c r="B11" s="2">
-        <v>208794608</v>
+        <v>115420544</v>
       </c>
       <c r="C11" s="2">
-        <v>637405023436800</v>
+        <v>169001795715072</v>
       </c>
       <c r="D11" s="1">
         <v>0.99102061986923218</v>
       </c>
       <c r="E11" s="2">
-        <v>216863072</v>
+        <v>118808696</v>
       </c>
       <c r="F11" s="1">
-        <v>11639880</v>
+        <v>6018884.5</v>
       </c>
       <c r="G11" s="1">
-        <v>0.039407268166542053</v>
+        <v>0.070250995457172394</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" t="s">
@@ -2893,22 +2893,22 @@
         <v>32705576</v>
       </c>
       <c r="B12" s="2">
-        <v>227335296</v>
+        <v>121562720</v>
       </c>
       <c r="C12" s="2">
-        <v>691825614520320</v>
+        <v>175493169020928</v>
       </c>
       <c r="D12" s="1">
-        <v>0.9920494556427002</v>
+        <v>0.99204891920089722</v>
       </c>
       <c r="E12" s="2">
-        <v>237643792</v>
+        <v>123639256</v>
       </c>
       <c r="F12" s="1">
-        <v>11639880</v>
+        <v>6018884.5</v>
       </c>
       <c r="G12" s="1">
-        <v>0.040424082428216934</v>
+        <v>0.074671193957328796</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" t="s">
@@ -2920,22 +2920,22 @@
         <v>32705576</v>
       </c>
       <c r="B13" s="2">
-        <v>250315344</v>
+        <v>127580576</v>
       </c>
       <c r="C13" s="2">
-        <v>759342433304576</v>
+        <v>183203608395776</v>
       </c>
       <c r="D13" s="1">
-        <v>0.99307841062545776</v>
+        <v>0.99307817220687866</v>
       </c>
       <c r="E13" s="2">
-        <v>262528016</v>
+        <v>129556104</v>
       </c>
       <c r="F13" s="1">
-        <v>11639880</v>
+        <v>6018884.5</v>
       </c>
       <c r="G13" s="1">
-        <v>0.042026635259389877</v>
+        <v>0.084009826183319092</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" t="s">
@@ -2947,22 +2947,22 @@
         <v>32705576</v>
       </c>
       <c r="B14" s="2">
-        <v>278168512</v>
+        <v>131497760</v>
       </c>
       <c r="C14" s="2">
-        <v>836963229761536</v>
+        <v>191586948349952</v>
       </c>
       <c r="D14" s="1">
         <v>0.99401366710662842</v>
       </c>
       <c r="E14" s="2">
-        <v>295120800</v>
+        <v>134941952</v>
       </c>
       <c r="F14" s="1">
-        <v>11639880</v>
+        <v>6018884.5</v>
       </c>
       <c r="G14" s="1">
-        <v>0.042234234511852264</v>
+        <v>0.086089245975017548</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" t="s">
@@ -2974,22 +2974,22 @@
         <v>32705576</v>
       </c>
       <c r="B15" s="2">
-        <v>315543072</v>
+        <v>142525728</v>
       </c>
       <c r="C15" s="2">
-        <v>949426210209792</v>
+        <v>203343901229056</v>
       </c>
       <c r="D15" s="1">
-        <v>0.99504262208938599</v>
+        <v>0.99504256248474121</v>
       </c>
       <c r="E15" s="2">
-        <v>340503904</v>
+        <v>144771104</v>
       </c>
       <c r="F15" s="1">
-        <v>11639880</v>
+        <v>6018884.5</v>
       </c>
       <c r="G15" s="1">
-        <v>0.043706510215997696</v>
+        <v>0.09630228579044342</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" t="s">
@@ -3001,22 +3001,22 @@
         <v>32705576</v>
       </c>
       <c r="B16" s="2">
-        <v>373363232</v>
+        <v>148184624</v>
       </c>
       <c r="C16" s="2">
-        <v>1108903177748480</v>
+        <v>218684601663488</v>
       </c>
       <c r="D16" s="1">
         <v>0.99607151746749878</v>
       </c>
       <c r="E16" s="2">
-        <v>403711168</v>
+        <v>151270208</v>
       </c>
       <c r="F16" s="1">
-        <v>11639880</v>
+        <v>6018884.5</v>
       </c>
       <c r="G16" s="1">
-        <v>0.040532369166612625</v>
+        <v>0.099340595304965973</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" t="s">
@@ -3028,22 +3028,22 @@
         <v>32705576</v>
       </c>
       <c r="B17" s="2">
-        <v>447935520</v>
+        <v>154936160</v>
       </c>
       <c r="C17" s="2">
-        <v>1329271574364160</v>
+        <v>239753026863104</v>
       </c>
       <c r="D17" s="1">
-        <v>0.99700683355331421</v>
+        <v>0.99700689315795899</v>
       </c>
       <c r="E17" s="2">
-        <v>504012000</v>
+        <v>166234336</v>
       </c>
       <c r="F17" s="1">
-        <v>11639880</v>
+        <v>6018884.5</v>
       </c>
       <c r="G17" s="1">
-        <v>0.038654502481222153</v>
+        <v>0.11243501305580139</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" t="s">
@@ -3055,22 +3055,22 @@
         <v>32705576</v>
       </c>
       <c r="B18" s="2">
-        <v>598365120</v>
+        <v>178993632</v>
       </c>
       <c r="C18" s="2">
-        <v>1761575601963008</v>
+        <v>278262743826432</v>
       </c>
       <c r="D18" s="1">
         <v>0.99803578853607178</v>
       </c>
       <c r="E18" s="2">
-        <v>752974400</v>
+        <v>193729616</v>
       </c>
       <c r="F18" s="1">
-        <v>11639880</v>
+        <v>6018884.5</v>
       </c>
       <c r="G18" s="1">
-        <v>0.037064094096422195</v>
+        <v>0.12651005387306213</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" t="s">
@@ -3082,22 +3082,22 @@
         <v>32705576</v>
       </c>
       <c r="B19" s="2">
-        <v>1044231232</v>
+        <v>218584048</v>
       </c>
       <c r="C19" s="2">
-        <v>2871033434472448</v>
+        <v>371248953556992</v>
       </c>
       <c r="D19" s="1">
         <v>0.99906468391418457</v>
       </c>
       <c r="E19" s="2">
-        <v>1091936512</v>
+        <v>222508752</v>
       </c>
       <c r="F19" s="1">
-        <v>11639880</v>
+        <v>6018884.5</v>
       </c>
       <c r="G19" s="1">
-        <v>0.031134206801652908</v>
+        <v>0.13584557175636292</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" t="s">
@@ -3109,22 +3109,22 @@
         <v>32705576</v>
       </c>
       <c r="B20" s="2">
-        <v>1248422016</v>
+        <v>233835968</v>
       </c>
       <c r="C20" s="2">
-        <v>3315789646004224</v>
+        <v>408432465149952</v>
       </c>
       <c r="D20" s="1">
         <v>0.99925172328948975</v>
       </c>
       <c r="E20" s="2">
-        <v>1319755264</v>
+        <v>245782416</v>
       </c>
       <c r="F20" s="1">
-        <v>11639880</v>
+        <v>6018884.5</v>
       </c>
       <c r="G20" s="1">
-        <v>0.028657224029302597</v>
+        <v>0.13664136826992035</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" t="s">
@@ -3136,22 +3136,22 @@
         <v>32705576</v>
       </c>
       <c r="B21" s="2">
-        <v>1570327680</v>
+        <v>260586672</v>
       </c>
       <c r="C21" s="2">
-        <v>3981242752040960</v>
+        <v>462658004320256</v>
       </c>
       <c r="D21" s="1">
         <v>0.9994388222694397</v>
       </c>
       <c r="E21" s="2">
-        <v>1695440000</v>
+        <v>277869440</v>
       </c>
       <c r="F21" s="1">
-        <v>11639880</v>
+        <v>6018884.5</v>
       </c>
       <c r="G21" s="1">
-        <v>0.026543557643890381</v>
+        <v>0.14248120784759522</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" t="s">
@@ -3163,22 +3163,22 @@
         <v>32705576</v>
       </c>
       <c r="B22" s="2">
-        <v>2164857600</v>
+        <v>319777568</v>
       </c>
       <c r="C22" s="2">
-        <v>5124144555360256</v>
+        <v>555052280315904</v>
       </c>
       <c r="D22" s="1">
         <v>0.99962586164474487</v>
       </c>
       <c r="E22" s="2">
-        <v>2449639168</v>
+        <v>329424608</v>
       </c>
       <c r="F22" s="1">
-        <v>11639880</v>
+        <v>6018884.5</v>
       </c>
       <c r="G22" s="1">
-        <v>0.022368401288986206</v>
+        <v>0.14429870247840881</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" t="s">
@@ -3190,22 +3190,22 @@
         <v>32705576</v>
       </c>
       <c r="B23" s="2">
-        <v>3879296000</v>
+        <v>451677952</v>
       </c>
       <c r="C23" s="2">
-        <v>7798649681608704</v>
+        <v>780680032157696</v>
       </c>
       <c r="D23" s="1">
         <v>0.99981296062469482</v>
       </c>
       <c r="E23" s="2">
-        <v>7798649856</v>
+        <v>780680000</v>
       </c>
       <c r="F23" s="1">
-        <v>11639880</v>
+        <v>6018884.5</v>
       </c>
       <c r="G23" s="1">
-        <v>0.016396239399909973</v>
+        <v>0.13620215654373169</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" t="s">
@@ -3255,22 +3255,22 @@
         <v>33679876</v>
       </c>
       <c r="B2" s="2">
-        <v>18868964</v>
+        <v>17241116</v>
       </c>
       <c r="C2" s="2">
-        <v>134979086450688</v>
+        <v>71173027135488</v>
       </c>
       <c r="D2" s="1">
         <v>0.91003322601318359</v>
       </c>
       <c r="E2" s="2">
-        <v>27588580</v>
+        <v>24095244</v>
       </c>
       <c r="F2" s="1">
-        <v>12211623</v>
+        <v>6464710</v>
       </c>
       <c r="G2" s="1">
-        <v>0.0029136913362890482</v>
+        <v>0.0033465384040027857</v>
       </c>
       <c r="H2" s="1">
         <v>2018</v>
@@ -3284,22 +3284,22 @@
         <v>33679876</v>
       </c>
       <c r="B3" s="2">
-        <v>36275080</v>
+        <v>31127794</v>
       </c>
       <c r="C3" s="2">
-        <v>148501463826432</v>
+        <v>77100803424256</v>
       </c>
       <c r="D3" s="1">
-        <v>0.92009472846984863</v>
+        <v>0.92009449005126953</v>
       </c>
       <c r="E3" s="2">
-        <v>43151364</v>
+        <v>37011756</v>
       </c>
       <c r="F3" s="1">
-        <v>12211623</v>
+        <v>6464710</v>
       </c>
       <c r="G3" s="1">
-        <v>0.0026813417207449675</v>
+        <v>0.0031482367776334286</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" t="s">
@@ -3311,22 +3311,22 @@
         <v>33679876</v>
       </c>
       <c r="B4" s="2">
-        <v>48511588</v>
+        <v>42264028</v>
       </c>
       <c r="C4" s="2">
-        <v>163508482211840</v>
+        <v>82836841299968</v>
       </c>
       <c r="D4" s="1">
-        <v>0.93005788326263428</v>
+        <v>0.93009644746780396</v>
       </c>
       <c r="E4" s="2">
-        <v>52602552</v>
+        <v>46213408</v>
       </c>
       <c r="F4" s="1">
-        <v>12211623</v>
+        <v>6464710</v>
       </c>
       <c r="G4" s="1">
-        <v>0.0022543005179613829</v>
+        <v>0.002608991926535964</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" t="s">
@@ -3338,22 +3338,22 @@
         <v>33679876</v>
       </c>
       <c r="B5" s="2">
-        <v>56938336</v>
+        <v>49832364</v>
       </c>
       <c r="C5" s="2">
-        <v>181933237600256</v>
+        <v>88929864777728</v>
       </c>
       <c r="D5" s="1">
-        <v>0.94002199172973633</v>
+        <v>0.94006741046905518</v>
       </c>
       <c r="E5" s="2">
-        <v>61409292</v>
+        <v>52797232</v>
       </c>
       <c r="F5" s="1">
-        <v>12211623</v>
+        <v>6464710</v>
       </c>
       <c r="G5" s="1">
-        <v>0.0037480802275240421</v>
+        <v>0.0045773410238325596</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" t="s">
@@ -3365,22 +3365,22 @@
         <v>33679876</v>
       </c>
       <c r="B6" s="2">
-        <v>66411400</v>
+        <v>56129392</v>
       </c>
       <c r="C6" s="2">
-        <v>206227082575872</v>
+        <v>96119967186944</v>
       </c>
       <c r="D6" s="1">
-        <v>0.95008361339569092</v>
+        <v>0.95001417398452759</v>
       </c>
       <c r="E6" s="2">
-        <v>72366848</v>
+        <v>60058124</v>
       </c>
       <c r="F6" s="1">
-        <v>12211623</v>
+        <v>6464710</v>
       </c>
       <c r="G6" s="1">
-        <v>0.0085312416777014732</v>
+        <v>0.010132473893463612</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" t="s">
@@ -3392,22 +3392,22 @@
         <v>33679876</v>
       </c>
       <c r="B7" s="2">
-        <v>79209848</v>
+        <v>63881248</v>
       </c>
       <c r="C7" s="2">
-        <v>239588140384256</v>
+        <v>105180813066240</v>
       </c>
       <c r="D7" s="1">
-        <v>0.96004205942153931</v>
+        <v>0.96005159616470337</v>
       </c>
       <c r="E7" s="2">
-        <v>87428280</v>
+        <v>68107296</v>
       </c>
       <c r="F7" s="1">
-        <v>12211623</v>
+        <v>6464710</v>
       </c>
       <c r="G7" s="1">
-        <v>0.013975675217807293</v>
+        <v>0.018374461680650711</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" t="s">
@@ -3419,22 +3419,22 @@
         <v>33679876</v>
       </c>
       <c r="B8" s="2">
-        <v>96911992</v>
+        <v>72193232</v>
       </c>
       <c r="C8" s="2">
-        <v>290166346350592</v>
+        <v>117519390081024</v>
       </c>
       <c r="D8" s="1">
-        <v>0.97001057863235474</v>
+        <v>0.97002696990966797</v>
       </c>
       <c r="E8" s="2">
-        <v>110011584</v>
+        <v>79026680</v>
       </c>
       <c r="F8" s="1">
-        <v>12211623</v>
+        <v>6464710</v>
       </c>
       <c r="G8" s="1">
-        <v>0.020206118002533913</v>
+        <v>0.027376759797334671</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" t="s">
@@ -3446,22 +3446,22 @@
         <v>33679876</v>
       </c>
       <c r="B9" s="2">
-        <v>126426152</v>
+        <v>91123912</v>
       </c>
       <c r="C9" s="2">
-        <v>381131102879744</v>
+        <v>136923725168640</v>
       </c>
       <c r="D9" s="1">
         <v>0.9800724983215332</v>
       </c>
       <c r="E9" s="2">
-        <v>156400688</v>
+        <v>103044680</v>
       </c>
       <c r="F9" s="1">
-        <v>12211623</v>
+        <v>6464710</v>
       </c>
       <c r="G9" s="1">
-        <v>0.033101502805948257</v>
+        <v>0.049498055130243301</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" t="s">
@@ -3473,22 +3473,22 @@
         <v>33679876</v>
       </c>
       <c r="B10" s="2">
-        <v>201894208</v>
+        <v>117717000</v>
       </c>
       <c r="C10" s="2">
-        <v>605861575655424</v>
+        <v>170802880184320</v>
       </c>
       <c r="D10" s="1">
         <v>0.9900362491607666</v>
       </c>
       <c r="E10" s="2">
-        <v>208382320</v>
+        <v>119511920</v>
       </c>
       <c r="F10" s="1">
-        <v>12211623</v>
+        <v>6464710</v>
       </c>
       <c r="G10" s="1">
-        <v>0.038717333227396011</v>
+        <v>0.065600551664829254</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" t="s">
@@ -3500,22 +3500,22 @@
         <v>33679876</v>
       </c>
       <c r="B11" s="2">
-        <v>216837232</v>
+        <v>121042584</v>
       </c>
       <c r="C11" s="2">
-        <v>649067537367040</v>
+        <v>176377110200320</v>
       </c>
       <c r="D11" s="1">
-        <v>0.99101310968399048</v>
+        <v>0.99101299047470093</v>
       </c>
       <c r="E11" s="2">
-        <v>225930992</v>
+        <v>123494200</v>
       </c>
       <c r="F11" s="1">
-        <v>12211623</v>
+        <v>6464710</v>
       </c>
       <c r="G11" s="1">
-        <v>0.039123449474573135</v>
+        <v>0.06873522698879242</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" t="s">
@@ -3527,22 +3527,22 @@
         <v>33679876</v>
       </c>
       <c r="B12" s="2">
-        <v>237376400</v>
+        <v>127899592</v>
       </c>
       <c r="C12" s="2">
-        <v>706527556009984</v>
+        <v>183559117602816</v>
       </c>
       <c r="D12" s="1">
-        <v>0.99208760261535645</v>
+        <v>0.99208754301071167</v>
       </c>
       <c r="E12" s="2">
-        <v>247300816</v>
+        <v>130239184</v>
       </c>
       <c r="F12" s="1">
-        <v>12211623</v>
+        <v>6464710</v>
       </c>
       <c r="G12" s="1">
-        <v>0.039926078170537949</v>
+        <v>0.074578486382961273</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" t="s">
@@ -3554,22 +3554,22 @@
         <v>33679876</v>
       </c>
       <c r="B13" s="2">
-        <v>260001824</v>
+        <v>133379168</v>
       </c>
       <c r="C13" s="2">
-        <v>771212179406848</v>
+        <v>191070277206016</v>
       </c>
       <c r="D13" s="1">
-        <v>0.9930645227432251</v>
+        <v>0.99306458234786987</v>
       </c>
       <c r="E13" s="2">
-        <v>272699808</v>
+        <v>135616944</v>
       </c>
       <c r="F13" s="1">
-        <v>12211623</v>
+        <v>6464710</v>
       </c>
       <c r="G13" s="1">
-        <v>0.041392028331756592</v>
+        <v>0.078901417553424835</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" t="s">
@@ -3581,22 +3581,22 @@
         <v>33679876</v>
       </c>
       <c r="B14" s="2">
-        <v>289339104</v>
+        <v>138576720</v>
       </c>
       <c r="C14" s="2">
-        <v>852933797216256</v>
+        <v>200159619186688</v>
       </c>
       <c r="D14" s="1">
-        <v>0.9940413236618042</v>
+        <v>0.99404126405715942</v>
       </c>
       <c r="E14" s="2">
-        <v>305352992</v>
+        <v>141133440</v>
       </c>
       <c r="F14" s="1">
-        <v>12211623</v>
+        <v>6464710</v>
       </c>
       <c r="G14" s="1">
-        <v>0.042277481406927109</v>
+        <v>0.087940312922000885</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" t="s">
@@ -3608,22 +3608,22 @@
         <v>33679876</v>
       </c>
       <c r="B15" s="2">
-        <v>326795648</v>
+        <v>148494288</v>
       </c>
       <c r="C15" s="2">
-        <v>960300060770304</v>
+        <v>211734639935488</v>
       </c>
       <c r="D15" s="1">
-        <v>0.9950181245803833</v>
+        <v>0.99501818418502808</v>
       </c>
       <c r="E15" s="2">
-        <v>351032256</v>
+        <v>151617360</v>
       </c>
       <c r="F15" s="1">
-        <v>12211623</v>
+        <v>6464710</v>
       </c>
       <c r="G15" s="1">
-        <v>0.044154331088066101</v>
+        <v>0.095084451138973236</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" t="s">
@@ -3635,22 +3635,22 @@
         <v>33679876</v>
       </c>
       <c r="B16" s="2">
-        <v>385170016</v>
+        <v>156068704</v>
       </c>
       <c r="C16" s="2">
-        <v>1127855861792768</v>
+        <v>228266673700864</v>
       </c>
       <c r="D16" s="1">
         <v>0.99609267711639404</v>
       </c>
       <c r="E16" s="2">
-        <v>419408352</v>
+        <v>159921344</v>
       </c>
       <c r="F16" s="1">
-        <v>12211623</v>
+        <v>6464710</v>
       </c>
       <c r="G16" s="1">
-        <v>0.04130597785115242</v>
+        <v>0.099748991429805756</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" t="s">
@@ -3662,22 +3662,22 @@
         <v>33679876</v>
       </c>
       <c r="B17" s="2">
-        <v>468499264</v>
+        <v>166313856</v>
       </c>
       <c r="C17" s="2">
-        <v>1363990613590016</v>
+        <v>251048002322432</v>
       </c>
       <c r="D17" s="1">
         <v>0.99706947803497315</v>
       </c>
       <c r="E17" s="2">
-        <v>523322272</v>
+        <v>178801440</v>
       </c>
       <c r="F17" s="1">
-        <v>12211623</v>
+        <v>6464710</v>
       </c>
       <c r="G17" s="1">
-        <v>0.039956048130989075</v>
+        <v>0.11045859754085541</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" t="s">
@@ -3689,22 +3689,22 @@
         <v>33679876</v>
       </c>
       <c r="B18" s="2">
-        <v>618265472</v>
+        <v>189391280</v>
       </c>
       <c r="C18" s="2">
-        <v>1784324701552640</v>
+        <v>287170170454016</v>
       </c>
       <c r="D18" s="1">
         <v>0.99804633855819702</v>
       </c>
       <c r="E18" s="2">
-        <v>763537664</v>
+        <v>205212064</v>
       </c>
       <c r="F18" s="1">
-        <v>12211623</v>
+        <v>6464710</v>
       </c>
       <c r="G18" s="1">
-        <v>0.038432631641626358</v>
+        <v>0.12847501039505005</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" t="s">
@@ -3716,22 +3716,22 @@
         <v>33679876</v>
       </c>
       <c r="B19" s="2">
-        <v>1031478144</v>
+        <v>230795936</v>
       </c>
       <c r="C19" s="2">
-        <v>2805174137520128</v>
+        <v>369133279510528</v>
       </c>
       <c r="D19" s="1">
         <v>0.9990231990814209</v>
       </c>
       <c r="E19" s="2">
-        <v>1075973888</v>
+        <v>238854016</v>
       </c>
       <c r="F19" s="1">
-        <v>12211623</v>
+        <v>6464710</v>
       </c>
       <c r="G19" s="1">
-        <v>0.035265639424324036</v>
+        <v>0.14135423302650452</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" t="s">
@@ -3743,22 +3743,22 @@
         <v>33679876</v>
       </c>
       <c r="B20" s="2">
-        <v>1232107392</v>
+        <v>254833520</v>
       </c>
       <c r="C20" s="2">
-        <v>3237490513149952</v>
+        <v>401704331771904</v>
       </c>
       <c r="D20" s="1">
         <v>0.99921858310699463</v>
       </c>
       <c r="E20" s="2">
-        <v>1299939584</v>
+        <v>256197504</v>
       </c>
       <c r="F20" s="1">
-        <v>12211623</v>
+        <v>6464710</v>
       </c>
       <c r="G20" s="1">
-        <v>0.031175140291452408</v>
+        <v>0.14022554457187653</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" t="s">
@@ -3770,22 +3770,22 @@
         <v>33679876</v>
       </c>
       <c r="B21" s="2">
-        <v>1545470592</v>
+        <v>269661696</v>
       </c>
       <c r="C21" s="2">
-        <v>3883373332267008</v>
+        <v>450209008058368</v>
       </c>
       <c r="D21" s="1">
         <v>0.99941390752792358</v>
       </c>
       <c r="E21" s="2">
-        <v>1666329088</v>
+        <v>279521376</v>
       </c>
       <c r="F21" s="1">
-        <v>12211623</v>
+        <v>6464710</v>
       </c>
       <c r="G21" s="1">
-        <v>0.027668766677379608</v>
+        <v>0.14468815922737122</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" t="s">
@@ -3797,22 +3797,22 @@
         <v>33679876</v>
       </c>
       <c r="B22" s="2">
-        <v>2127991168</v>
+        <v>334366048</v>
       </c>
       <c r="C22" s="2">
-        <v>4991979821727744</v>
+        <v>535559369916416</v>
       </c>
       <c r="D22" s="1">
         <v>0.99960929155349732</v>
       </c>
       <c r="E22" s="2">
-        <v>2408417024</v>
+        <v>336588000</v>
       </c>
       <c r="F22" s="1">
-        <v>12211623</v>
+        <v>6464710</v>
       </c>
       <c r="G22" s="1">
-        <v>0.024190908297896385</v>
+        <v>0.14951774477958679</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" t="s">
@@ -3824,22 +3824,22 @@
         <v>33679876</v>
       </c>
       <c r="B23" s="2">
-        <v>3790356992</v>
+        <v>449318816</v>
       </c>
       <c r="C23" s="2">
-        <v>7575935226216448</v>
+        <v>734560874659840</v>
       </c>
       <c r="D23" s="1">
         <v>0.99980467557907105</v>
       </c>
       <c r="E23" s="2">
-        <v>7575934976</v>
+        <v>734560896</v>
       </c>
       <c r="F23" s="1">
-        <v>12211623</v>
+        <v>6464710</v>
       </c>
       <c r="G23" s="1">
-        <v>0.018047519028186798</v>
+        <v>0.15034963190555573</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" t="s">
@@ -3889,22 +3889,22 @@
         <v>34643400</v>
       </c>
       <c r="B2" s="2">
-        <v>11572790</v>
+        <v>10837283</v>
       </c>
       <c r="C2" s="2">
-        <v>129876942127104</v>
+        <v>69169559109632</v>
       </c>
       <c r="D2" s="1">
         <v>0.90007615089416504</v>
       </c>
       <c r="E2" s="2">
-        <v>21638402</v>
+        <v>19471762</v>
       </c>
       <c r="F2" s="1">
-        <v>12997715</v>
+        <v>6929130.5</v>
       </c>
       <c r="G2" s="1">
-        <v>0.00046175744500942528</v>
+        <v>0.00051221507601439953</v>
       </c>
       <c r="H2" s="1">
         <v>2019</v>
@@ -3918,22 +3918,22 @@
         <v>34643400</v>
       </c>
       <c r="B3" s="2">
-        <v>30630190</v>
+        <v>27556560</v>
       </c>
       <c r="C3" s="2">
-        <v>141819350351872</v>
+        <v>74652932112384</v>
       </c>
       <c r="D3" s="1">
         <v>0.91000562906265259</v>
       </c>
       <c r="E3" s="2">
-        <v>37757824</v>
+        <v>33614916</v>
       </c>
       <c r="F3" s="1">
-        <v>12997715</v>
+        <v>6929130.5</v>
       </c>
       <c r="G3" s="1">
-        <v>0.00059412239352241159</v>
+        <v>0.00080662802793085575</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" t="s">
@@ -3945,22 +3945,22 @@
         <v>34643400</v>
       </c>
       <c r="B4" s="2">
-        <v>44268308</v>
+        <v>39102736</v>
       </c>
       <c r="C4" s="2">
-        <v>154878080974848</v>
+        <v>79820079759360</v>
       </c>
       <c r="D4" s="1">
-        <v>0.92003989219665527</v>
+        <v>0.92006975412368775</v>
       </c>
       <c r="E4" s="2">
-        <v>48935224</v>
+        <v>43145152</v>
       </c>
       <c r="F4" s="1">
-        <v>12997715</v>
+        <v>6929130.5</v>
       </c>
       <c r="G4" s="1">
-        <v>0.0012012382503598928</v>
+        <v>0.0014016380300745368</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" t="s">
@@ -3972,22 +3972,22 @@
         <v>34643400</v>
       </c>
       <c r="B5" s="2">
-        <v>52940072</v>
+        <v>46765596</v>
       </c>
       <c r="C5" s="2">
-        <v>170079815729152</v>
+        <v>85066441031680</v>
       </c>
       <c r="D5" s="1">
-        <v>0.93007361888885498</v>
+        <v>0.9300728440284729</v>
       </c>
       <c r="E5" s="2">
-        <v>57025096</v>
+        <v>50053296</v>
       </c>
       <c r="F5" s="1">
-        <v>12997715</v>
+        <v>6929130.5</v>
       </c>
       <c r="G5" s="1">
-        <v>0.0020132798235863447</v>
+        <v>0.0022521698847413063</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" t="s">
@@ -3999,22 +3999,22 @@
         <v>34643400</v>
       </c>
       <c r="B6" s="2">
-        <v>61301960</v>
+        <v>53066848</v>
       </c>
       <c r="C6" s="2">
-        <v>188790622650368</v>
+        <v>90867792609280</v>
       </c>
       <c r="D6" s="1">
-        <v>0.94000321626663208</v>
+        <v>0.94001227617263794</v>
       </c>
       <c r="E6" s="2">
-        <v>65810080</v>
+        <v>56117888</v>
       </c>
       <c r="F6" s="1">
-        <v>12997715</v>
+        <v>6929130.5</v>
       </c>
       <c r="G6" s="1">
-        <v>0.0046322885900735855</v>
+        <v>0.0054398500360548496</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" t="s">
@@ -4026,22 +4026,22 @@
         <v>34643400</v>
       </c>
       <c r="B7" s="2">
-        <v>70852720</v>
+        <v>59518756</v>
       </c>
       <c r="C7" s="2">
-        <v>213489771610112</v>
+        <v>97840151920640</v>
       </c>
       <c r="D7" s="1">
-        <v>0.95003753900527954</v>
+        <v>0.95003706216812134</v>
       </c>
       <c r="E7" s="2">
-        <v>77021136</v>
+        <v>63003196</v>
       </c>
       <c r="F7" s="1">
-        <v>12997715</v>
+        <v>6929130.5</v>
       </c>
       <c r="G7" s="1">
-        <v>0.010105748660862446</v>
+        <v>0.01232418604195118</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" t="s">
@@ -4053,22 +4053,22 @@
         <v>34643400</v>
       </c>
       <c r="B8" s="2">
-        <v>84072792</v>
+        <v>66485876</v>
       </c>
       <c r="C8" s="2">
-        <v>247784783478784</v>
+        <v>106596977868800</v>
       </c>
       <c r="D8" s="1">
-        <v>0.96007168292999268</v>
+        <v>0.96007323265075684</v>
       </c>
       <c r="E8" s="2">
-        <v>92556368</v>
+        <v>71005080</v>
       </c>
       <c r="F8" s="1">
-        <v>12997715</v>
+        <v>6929130.5</v>
       </c>
       <c r="G8" s="1">
-        <v>0.01516744215041399</v>
+        <v>0.020369935780763626</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" t="s">
@@ -4080,22 +4080,22 @@
         <v>34643400</v>
       </c>
       <c r="B9" s="2">
-        <v>102064432</v>
+        <v>75179048</v>
       </c>
       <c r="C9" s="2">
-        <v>299168060932096</v>
+        <v>118376068284416</v>
       </c>
       <c r="D9" s="1">
-        <v>0.97000163793563843</v>
+        <v>0.97000128030776978</v>
       </c>
       <c r="E9" s="2">
-        <v>115865448</v>
+        <v>81886792</v>
       </c>
       <c r="F9" s="1">
-        <v>12997715</v>
+        <v>6929130.5</v>
       </c>
       <c r="G9" s="1">
-        <v>0.02141517773270607</v>
+        <v>0.029462290927767754</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" t="s">
@@ -4107,22 +4107,22 @@
         <v>34643400</v>
       </c>
       <c r="B10" s="2">
-        <v>133197528</v>
+        <v>93514920</v>
       </c>
       <c r="C10" s="2">
-        <v>391300411031552</v>
+        <v>136718531428352</v>
       </c>
       <c r="D10" s="1">
-        <v>0.98003602027893067</v>
+        <v>0.98003655672073364</v>
       </c>
       <c r="E10" s="2">
-        <v>164542304</v>
+        <v>105333520</v>
       </c>
       <c r="F10" s="1">
-        <v>12997715</v>
+        <v>6929130.5</v>
       </c>
       <c r="G10" s="1">
-        <v>0.035045720636844635</v>
+        <v>0.053602594882249832</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" t="s">
@@ -4134,22 +4134,22 @@
         <v>34643400</v>
       </c>
       <c r="B11" s="2">
-        <v>212269120</v>
+        <v>119939280</v>
       </c>
       <c r="C11" s="2">
-        <v>620447418810368</v>
+        <v>168432544776192</v>
       </c>
       <c r="D11" s="1">
         <v>0.99007034301757813</v>
       </c>
       <c r="E11" s="2">
-        <v>219111712</v>
+        <v>121836208</v>
       </c>
       <c r="F11" s="1">
-        <v>12997715</v>
+        <v>6929130.5</v>
       </c>
       <c r="G11" s="1">
-        <v>0.040303111076354981</v>
+        <v>0.070260792970657349</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" t="s">
@@ -4161,22 +4161,22 @@
         <v>34643400</v>
       </c>
       <c r="B12" s="2">
-        <v>228130032</v>
+        <v>124071096</v>
       </c>
       <c r="C12" s="2">
-        <v>662435824402432</v>
+        <v>173308507062272</v>
       </c>
       <c r="D12" s="1">
-        <v>0.99101078510284424</v>
+        <v>0.99101096391677857</v>
       </c>
       <c r="E12" s="2">
-        <v>236696656</v>
+        <v>125756504</v>
       </c>
       <c r="F12" s="1">
-        <v>12997715</v>
+        <v>6929130.5</v>
       </c>
       <c r="G12" s="1">
-        <v>0.040612787008285523</v>
+        <v>0.073555760085582733</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" t="s">
@@ -4188,22 +4188,22 @@
         <v>34643400</v>
       </c>
       <c r="B13" s="2">
-        <v>248009648</v>
+        <v>129449800</v>
       </c>
       <c r="C13" s="2">
-        <v>718467699310592</v>
+        <v>179565838204928</v>
       </c>
       <c r="D13" s="1">
         <v>0.99205625057220459</v>
       </c>
       <c r="E13" s="2">
-        <v>259173456</v>
+        <v>130657840</v>
       </c>
       <c r="F13" s="1">
-        <v>12997715</v>
+        <v>6929130.5</v>
       </c>
       <c r="G13" s="1">
-        <v>0.041340947151184082</v>
+        <v>0.079448610544204712</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" t="s">
@@ -4215,22 +4215,22 @@
         <v>34643400</v>
       </c>
       <c r="B14" s="2">
-        <v>273128928</v>
+        <v>134187072</v>
       </c>
       <c r="C14" s="2">
-        <v>788054893658112</v>
+        <v>186977727021056</v>
       </c>
       <c r="D14" s="1">
-        <v>0.99310147762298584</v>
+        <v>0.99310171604156494</v>
       </c>
       <c r="E14" s="2">
-        <v>285367232</v>
+        <v>136334624</v>
       </c>
       <c r="F14" s="1">
-        <v>12997715</v>
+        <v>6929130.5</v>
       </c>
       <c r="G14" s="1">
-        <v>0.042402900755405426</v>
+        <v>0.083965346217155457</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" t="s">
@@ -4242,22 +4242,22 @@
         <v>34643400</v>
       </c>
       <c r="B15" s="2">
-        <v>301382912</v>
+        <v>140145312</v>
       </c>
       <c r="C15" s="2">
-        <v>867431190888448</v>
+        <v>194972489875456</v>
       </c>
       <c r="D15" s="1">
         <v>0.99404221773147583</v>
       </c>
       <c r="E15" s="2">
-        <v>319399168</v>
+        <v>142655024</v>
       </c>
       <c r="F15" s="1">
-        <v>12997715</v>
+        <v>6929130.5</v>
       </c>
       <c r="G15" s="1">
-        <v>0.043095212429761887</v>
+        <v>0.092955909669399261</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" t="s">
@@ -4269,22 +4269,22 @@
         <v>34643400</v>
       </c>
       <c r="B16" s="2">
-        <v>343123136</v>
+        <v>145765584</v>
       </c>
       <c r="C16" s="2">
-        <v>984033043415040</v>
+        <v>206103803592704</v>
       </c>
       <c r="D16" s="1">
         <v>0.99508744478225708</v>
       </c>
       <c r="E16" s="2">
-        <v>363813408</v>
+        <v>151971008</v>
       </c>
       <c r="F16" s="1">
-        <v>12997715</v>
+        <v>6929130.5</v>
       </c>
       <c r="G16" s="1">
-        <v>0.045939598232507706</v>
+        <v>0.10165400058031082</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" t="s">
@@ -4296,22 +4296,22 @@
         <v>34643400</v>
       </c>
       <c r="B17" s="2">
-        <v>393816576</v>
+        <v>156500144</v>
       </c>
       <c r="C17" s="2">
-        <v>1130926092320768</v>
+        <v>218925119832064</v>
       </c>
       <c r="D17" s="1">
-        <v>0.99602812528610229</v>
+        <v>0.99602818489074707</v>
       </c>
       <c r="E17" s="2">
-        <v>429469184</v>
+        <v>159608144</v>
       </c>
       <c r="F17" s="1">
-        <v>12997715</v>
+        <v>6929130.5</v>
       </c>
       <c r="G17" s="1">
-        <v>0.04303356260061264</v>
+        <v>0.10685494542121887</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" t="s">
@@ -4323,22 +4323,22 @@
         <v>34643400</v>
       </c>
       <c r="B18" s="2">
-        <v>480206944</v>
+        <v>165655264</v>
       </c>
       <c r="C18" s="2">
-        <v>1381453279526912</v>
+        <v>240109760806912</v>
       </c>
       <c r="D18" s="1">
         <v>0.99707335233688355</v>
       </c>
       <c r="E18" s="2">
-        <v>531484928</v>
+        <v>177272464</v>
       </c>
       <c r="F18" s="1">
-        <v>12997715</v>
+        <v>6929130.5</v>
       </c>
       <c r="G18" s="1">
-        <v>0.0425751693546772</v>
+        <v>0.11882581561803818</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" t="s">
@@ -4350,22 +4350,22 @@
         <v>34643400</v>
       </c>
       <c r="B19" s="2">
-        <v>619846656</v>
+        <v>186569440</v>
       </c>
       <c r="C19" s="2">
-        <v>1784069822087168</v>
+        <v>269874790137856</v>
       </c>
       <c r="D19" s="1">
         <v>0.99801409244537354</v>
       </c>
       <c r="E19" s="2">
-        <v>797599936</v>
+        <v>198276144</v>
       </c>
       <c r="F19" s="1">
-        <v>12997715</v>
+        <v>6929130.5</v>
       </c>
       <c r="G19" s="1">
-        <v>0.039665382355451584</v>
+        <v>0.14093506336212158</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" t="s">
@@ -4377,22 +4377,22 @@
         <v>34643400</v>
       </c>
       <c r="B20" s="2">
-        <v>1160227200</v>
+        <v>226205984</v>
       </c>
       <c r="C20" s="2">
-        <v>3140466128191488</v>
+        <v>368322939977728</v>
       </c>
       <c r="D20" s="1">
         <v>0.99916380643844605</v>
       </c>
       <c r="E20" s="2">
-        <v>1222967296</v>
+        <v>231728032</v>
       </c>
       <c r="F20" s="1">
-        <v>12997715</v>
+        <v>6929130.5</v>
       </c>
       <c r="G20" s="1">
-        <v>0.035440489649772644</v>
+        <v>0.16692966222763062</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" t="s">
@@ -4404,22 +4404,22 @@
         <v>34643400</v>
       </c>
       <c r="B21" s="2">
-        <v>1448856064</v>
+        <v>245628160</v>
       </c>
       <c r="C21" s="2">
-        <v>3779632692199424</v>
+        <v>413854592925696</v>
       </c>
       <c r="D21" s="1">
         <v>0.99937283992767334</v>
       </c>
       <c r="E21" s="2">
-        <v>1560294656</v>
+        <v>255802880</v>
       </c>
       <c r="F21" s="1">
-        <v>12997715</v>
+        <v>6929130.5</v>
       </c>
       <c r="G21" s="1">
-        <v>0.03249678760766983</v>
+        <v>0.16521260142326355</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" t="s">
@@ -4431,22 +4431,22 @@
         <v>34643400</v>
       </c>
       <c r="B22" s="2">
-        <v>2003166976</v>
+        <v>279320992</v>
       </c>
       <c r="C22" s="2">
-        <v>4889301649195008</v>
+        <v>492880447668224</v>
       </c>
       <c r="D22" s="1">
         <v>0.99958193302154541</v>
       </c>
       <c r="E22" s="2">
-        <v>2272632320</v>
+        <v>293049472</v>
       </c>
       <c r="F22" s="1">
-        <v>12997715</v>
+        <v>6929130.5</v>
       </c>
       <c r="G22" s="1">
-        <v>0.027836818248033524</v>
+        <v>0.18049910664558411</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" t="s">
@@ -4458,22 +4458,22 @@
         <v>34643400</v>
       </c>
       <c r="B23" s="2">
-        <v>3637841152</v>
+        <v>390853120</v>
       </c>
       <c r="C23" s="2">
-        <v>7505970745835520</v>
+        <v>692711451525120</v>
       </c>
       <c r="D23" s="1">
         <v>0.99979096651077271</v>
       </c>
       <c r="E23" s="2">
-        <v>7505970176</v>
+        <v>692711424</v>
       </c>
       <c r="F23" s="1">
-        <v>12997715</v>
+        <v>6929130.5</v>
       </c>
       <c r="G23" s="1">
-        <v>0.020835340023040771</v>
+        <v>0.17796653509140015</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" t="s">
@@ -4486,7 +4486,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4523,22 +4523,22 @@
         <v>35465232</v>
       </c>
       <c r="B2" s="2">
-        <v>1234684.125</v>
+        <v>21308890</v>
       </c>
       <c r="C2" s="2">
-        <v>118434713042944</v>
+        <v>72205564116992</v>
       </c>
       <c r="D2" s="1">
-        <v>0.89003574848175049</v>
+        <v>0.90001267194747925</v>
       </c>
       <c r="E2" s="2">
-        <v>13839710</v>
+        <v>27473776</v>
       </c>
       <c r="F2" s="1">
-        <v>13023777</v>
+        <v>7345124.5</v>
       </c>
       <c r="G2" s="1">
-        <v>0.00037170693394728005</v>
+        <v>0.00010064633534057066</v>
       </c>
       <c r="H2" s="1">
         <v>2020</v>
@@ -4552,22 +4552,22 @@
         <v>35465232</v>
       </c>
       <c r="B3" s="2">
-        <v>23234040</v>
+        <v>33408962</v>
       </c>
       <c r="C3" s="2">
-        <v>128871433240576</v>
+        <v>77223973355520</v>
       </c>
       <c r="D3" s="1">
-        <v>0.90001267194747925</v>
+        <v>0.9100986123085022</v>
       </c>
       <c r="E3" s="2">
-        <v>30219234</v>
+        <v>37904692</v>
       </c>
       <c r="F3" s="1">
-        <v>13023777</v>
+        <v>7345124.5</v>
       </c>
       <c r="G3" s="1">
-        <v>9.1200919996481389e-05</v>
+        <v>0.00078340602340176702</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" t="s">
@@ -4579,22 +4579,22 @@
         <v>35465232</v>
       </c>
       <c r="B4" s="2">
-        <v>36805220</v>
+        <v>42372416</v>
       </c>
       <c r="C4" s="2">
-        <v>139941283627008</v>
+        <v>82132005289984</v>
       </c>
       <c r="D4" s="1">
-        <v>0.91010040044784546</v>
+        <v>0.92007523775100708</v>
       </c>
       <c r="E4" s="2">
-        <v>41903308</v>
+        <v>45398860</v>
       </c>
       <c r="F4" s="1">
-        <v>13023777</v>
+        <v>7345124.5</v>
       </c>
       <c r="G4" s="1">
-        <v>0.00070044706808403134</v>
+        <v>0.0013312867376953363</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" t="s">
@@ -4606,22 +4606,22 @@
         <v>35465232</v>
       </c>
       <c r="B5" s="2">
-        <v>47047860</v>
+        <v>48982080</v>
       </c>
       <c r="C5" s="2">
-        <v>152179616776192</v>
+        <v>87372855246848</v>
       </c>
       <c r="D5" s="1">
-        <v>0.920077383518219</v>
+        <v>0.93005460500717163</v>
       </c>
       <c r="E5" s="2">
-        <v>51074496</v>
+        <v>51661072</v>
       </c>
       <c r="F5" s="1">
-        <v>13023777</v>
+        <v>7345124.5</v>
       </c>
       <c r="G5" s="1">
-        <v>0.0011573371011763811</v>
+        <v>0.0021996593568474054</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" t="s">
@@ -4633,22 +4633,22 @@
         <v>35465232</v>
       </c>
       <c r="B6" s="2">
-        <v>54849792</v>
+        <v>54630492</v>
       </c>
       <c r="C6" s="2">
-        <v>166598828621824</v>
+        <v>93312467861504</v>
       </c>
       <c r="D6" s="1">
-        <v>0.93005293607711792</v>
+        <v>0.94002902507781982</v>
       </c>
       <c r="E6" s="2">
-        <v>58813184</v>
+        <v>57760976</v>
       </c>
       <c r="F6" s="1">
-        <v>13023777</v>
+        <v>7345124.5</v>
       </c>
       <c r="G6" s="1">
-        <v>0.0019341743318364024</v>
+        <v>0.0047533097676932812</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" t="s">
@@ -4660,22 +4660,22 @@
         <v>35465232</v>
       </c>
       <c r="B7" s="2">
-        <v>63045648</v>
+        <v>61154740</v>
       </c>
       <c r="C7" s="2">
-        <v>184530820399104</v>
+        <v>100415907561472</v>
       </c>
       <c r="D7" s="1">
-        <v>0.94002997875213623</v>
+        <v>0.95001614093780518</v>
       </c>
       <c r="E7" s="2">
-        <v>67548280</v>
+        <v>64575828</v>
       </c>
       <c r="F7" s="1">
-        <v>13023777</v>
+        <v>7345124.5</v>
       </c>
       <c r="G7" s="1">
-        <v>0.0039875688962638378</v>
+        <v>0.011271337047219276</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" t="s">
@@ -4687,22 +4687,22 @@
         <v>35465232</v>
       </c>
       <c r="B8" s="2">
-        <v>72408312</v>
+        <v>68052760</v>
       </c>
       <c r="C8" s="2">
-        <v>207874974285824</v>
+        <v>109483279777792</v>
       </c>
       <c r="D8" s="1">
-        <v>0.95000630617141724</v>
+        <v>0.96010851860046387</v>
       </c>
       <c r="E8" s="2">
-        <v>78342464</v>
+        <v>72690088</v>
       </c>
       <c r="F8" s="1">
-        <v>13023777</v>
+        <v>7345124.5</v>
       </c>
       <c r="G8" s="1">
-        <v>0.0092853009700775146</v>
+        <v>0.019456781446933746</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" t="s">
@@ -4714,22 +4714,22 @@
         <v>35465232</v>
       </c>
       <c r="B9" s="2">
-        <v>85088600</v>
+        <v>78912184</v>
       </c>
       <c r="C9" s="2">
-        <v>240619704287232</v>
+        <v>121736016166912</v>
       </c>
       <c r="D9" s="1">
-        <v>0.96009421348571777</v>
+        <v>0.97007429599761963</v>
       </c>
       <c r="E9" s="2">
-        <v>93559760</v>
+        <v>83562272</v>
       </c>
       <c r="F9" s="1">
-        <v>13023777</v>
+        <v>7345124.5</v>
       </c>
       <c r="G9" s="1">
-        <v>0.014628463424742222</v>
+        <v>0.026752477511763573</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" t="s">
@@ -4741,22 +4741,22 @@
         <v>35465232</v>
       </c>
       <c r="B10" s="2">
-        <v>103084480</v>
+        <v>94593832</v>
       </c>
       <c r="C10" s="2">
-        <v>289642024796160</v>
+        <v>140818824298496</v>
       </c>
       <c r="D10" s="1">
-        <v>0.97007101774215698</v>
+        <v>0.98004812002182007</v>
       </c>
       <c r="E10" s="2">
-        <v>115863760</v>
+        <v>107497584</v>
       </c>
       <c r="F10" s="1">
-        <v>13023777</v>
+        <v>7345124.5</v>
       </c>
       <c r="G10" s="1">
-        <v>0.019930940121412277</v>
+        <v>0.05020102858543396</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" t="s">
@@ -4768,22 +4768,22 @@
         <v>35465232</v>
       </c>
       <c r="B11" s="2">
-        <v>132491576</v>
+        <v>123281400</v>
       </c>
       <c r="C11" s="2">
-        <v>376530052055040</v>
+        <v>174136932433920</v>
       </c>
       <c r="D11" s="1">
-        <v>0.98004722595214844</v>
+        <v>0.99002355337142944</v>
       </c>
       <c r="E11" s="2">
-        <v>161312480</v>
+        <v>123776496</v>
       </c>
       <c r="F11" s="1">
-        <v>13023777</v>
+        <v>7345124.5</v>
       </c>
       <c r="G11" s="1">
-        <v>0.033949006348848343</v>
+        <v>0.066934049129486084</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" t="s">
@@ -4795,22 +4795,22 @@
         <v>35465232</v>
       </c>
       <c r="B12" s="2">
-        <v>205555536</v>
+        <v>126092784</v>
       </c>
       <c r="C12" s="2">
-        <v>591747038052352</v>
+        <v>179803151925248</v>
       </c>
       <c r="D12" s="1">
-        <v>0.99002361297607422</v>
+        <v>0.99103254079818726</v>
       </c>
       <c r="E12" s="2">
-        <v>212038720</v>
+        <v>127315392</v>
       </c>
       <c r="F12" s="1">
-        <v>13023777</v>
+        <v>7345124.5</v>
       </c>
       <c r="G12" s="1">
-        <v>0.040319833904504776</v>
+        <v>0.06991143524646759</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" t="s">
@@ -4822,22 +4822,22 @@
         <v>35465232</v>
       </c>
       <c r="B13" s="2">
-        <v>220732192</v>
+        <v>130874240</v>
       </c>
       <c r="C13" s="2">
-        <v>634466728935424</v>
+        <v>186456173707264</v>
       </c>
       <c r="D13" s="1">
-        <v>0.99103254079818726</v>
+        <v>0.99204134941101074</v>
       </c>
       <c r="E13" s="2">
-        <v>228737104</v>
+        <v>133176008</v>
       </c>
       <c r="F13" s="1">
-        <v>13023777</v>
+        <v>7345124.5</v>
       </c>
       <c r="G13" s="1">
-        <v>0.040482118725776672</v>
+        <v>0.074990123510360718</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" t="s">
@@ -4849,22 +4849,22 @@
         <v>35465232</v>
       </c>
       <c r="B14" s="2">
-        <v>239483232</v>
+        <v>136013856</v>
       </c>
       <c r="C14" s="2">
-        <v>685899230740480</v>
+        <v>194190654832640</v>
       </c>
       <c r="D14" s="1">
-        <v>0.99204140901565552</v>
+        <v>0.993050217628479</v>
       </c>
       <c r="E14" s="2">
-        <v>248794720</v>
+        <v>137783008</v>
       </c>
       <c r="F14" s="1">
-        <v>13023777</v>
+        <v>7345124.5</v>
       </c>
       <c r="G14" s="1">
-        <v>0.04131559282541275</v>
+        <v>0.07994687557220459</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" t="s">
@@ -4876,22 +4876,22 @@
         <v>35465232</v>
       </c>
       <c r="B15" s="2">
-        <v>261472896</v>
+        <v>141337392</v>
       </c>
       <c r="C15" s="2">
-        <v>749348447059968</v>
+        <v>203769388204032</v>
       </c>
       <c r="D15" s="1">
-        <v>0.993050217628479</v>
+        <v>0.99405902624130249</v>
       </c>
       <c r="E15" s="2">
-        <v>274163616</v>
+        <v>144965504</v>
       </c>
       <c r="F15" s="1">
-        <v>13023777</v>
+        <v>7345124.5</v>
       </c>
       <c r="G15" s="1">
-        <v>0.041925471276044846</v>
+        <v>0.086942575871944427</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" t="s">
@@ -4903,22 +4903,22 @@
         <v>35465232</v>
       </c>
       <c r="B16" s="2">
-        <v>290912768</v>
+        <v>150539888</v>
       </c>
       <c r="C16" s="2">
-        <v>830040816222208</v>
+        <v>215797158903808</v>
       </c>
       <c r="D16" s="1">
-        <v>0.99405902624130249</v>
+        <v>0.99506789445877075</v>
       </c>
       <c r="E16" s="2">
-        <v>306276960</v>
+        <v>153324384</v>
       </c>
       <c r="F16" s="1">
-        <v>13023777</v>
+        <v>7345124.5</v>
       </c>
       <c r="G16" s="1">
-        <v>0.043011736124753952</v>
+        <v>0.094932578504085541</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" t="s">
@@ -4930,22 +4930,22 @@
         <v>35465232</v>
       </c>
       <c r="B17" s="2">
-        <v>328209792</v>
+        <v>159995152</v>
       </c>
       <c r="C17" s="2">
-        <v>937171728990208</v>
+        <v>231861645213696</v>
       </c>
       <c r="D17" s="1">
-        <v>0.99506789445877075</v>
+        <v>0.99607670307159424</v>
       </c>
       <c r="E17" s="2">
-        <v>350504064</v>
+        <v>164195664</v>
       </c>
       <c r="F17" s="1">
-        <v>13023777</v>
+        <v>7345124.5</v>
       </c>
       <c r="G17" s="1">
-        <v>0.043940853327512741</v>
+        <v>0.10213737934827805</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" t="s">
@@ -4957,22 +4957,22 @@
         <v>35465232</v>
       </c>
       <c r="B18" s="2">
-        <v>382085088</v>
+        <v>168987840</v>
       </c>
       <c r="C18" s="2">
-        <v>1088035072507904</v>
+        <v>255285507653632</v>
       </c>
       <c r="D18" s="1">
-        <v>0.99607676267623901</v>
+        <v>0.9970855712890625</v>
       </c>
       <c r="E18" s="2">
-        <v>413135072</v>
+        <v>184250784</v>
       </c>
       <c r="F18" s="1">
-        <v>13023777</v>
+        <v>7345124.5</v>
       </c>
       <c r="G18" s="1">
-        <v>0.043348178267478943</v>
+        <v>0.11156893521547318</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" t="s">
@@ -4984,22 +4984,22 @@
         <v>35465232</v>
       </c>
       <c r="B19" s="2">
-        <v>460269312</v>
+        <v>195763280</v>
       </c>
       <c r="C19" s="2">
-        <v>1321657671090176</v>
+        <v>292891368882176</v>
       </c>
       <c r="D19" s="1">
-        <v>0.9970855712890625</v>
+        <v>0.99809443950653076</v>
       </c>
       <c r="E19" s="2">
-        <v>512992192</v>
+        <v>209229808</v>
       </c>
       <c r="F19" s="1">
-        <v>13023777</v>
+        <v>7345124.5</v>
       </c>
       <c r="G19" s="1">
-        <v>0.043111559003591538</v>
+        <v>0.13169223070144653</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" t="s">
@@ -5011,22 +5011,22 @@
         <v>35465232</v>
       </c>
       <c r="B20" s="2">
-        <v>607658368</v>
+        <v>238037168</v>
       </c>
       <c r="C20" s="2">
-        <v>1749766455164928</v>
+        <v>387012255285248</v>
       </c>
       <c r="D20" s="1">
-        <v>0.99809443950653076</v>
+        <v>0.99910324811935425</v>
       </c>
       <c r="E20" s="2">
-        <v>756808960</v>
+        <v>241976016</v>
       </c>
       <c r="F20" s="1">
-        <v>13023777</v>
+        <v>7345124.5</v>
       </c>
       <c r="G20" s="1">
-        <v>0.040660012513399124</v>
+        <v>0.14814381301403046</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" t="s">
@@ -5038,22 +5038,22 @@
         <v>35465232</v>
       </c>
       <c r="B21" s="2">
-        <v>1048180416</v>
+        <v>263253136</v>
       </c>
       <c r="C21" s="2">
-        <v>2866863021228032</v>
+        <v>435359695503360</v>
       </c>
       <c r="D21" s="1">
-        <v>0.99910324811935425</v>
+        <v>0.99932748079299927</v>
       </c>
       <c r="E21" s="2">
-        <v>1106447104</v>
+        <v>268753792</v>
       </c>
       <c r="F21" s="1">
-        <v>13023777</v>
+        <v>7345124.5</v>
       </c>
       <c r="G21" s="1">
-        <v>0.036707356572151184</v>
+        <v>0.15544717013835907</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" t="s">
@@ -5065,22 +5065,22 @@
         <v>35465232</v>
       </c>
       <c r="B22" s="2">
-        <v>1311814656</v>
+        <v>309715552</v>
       </c>
       <c r="C22" s="2">
-        <v>3453692992815104</v>
+        <v>518667901075456</v>
       </c>
       <c r="D22" s="1">
-        <v>0.99932748079299927</v>
+        <v>0.99955165386199951</v>
       </c>
       <c r="E22" s="2">
-        <v>1412396672</v>
+        <v>328050848</v>
       </c>
       <c r="F22" s="1">
-        <v>13023777</v>
+        <v>7345124.5</v>
       </c>
       <c r="G22" s="1">
-        <v>0.033884212374687195</v>
+        <v>0.1610887199640274</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" t="s">
@@ -5092,52 +5092,25 @@
         <v>35465232</v>
       </c>
       <c r="B23" s="2">
-        <v>1813872000</v>
+        <v>414722176</v>
       </c>
       <c r="C23" s="2">
-        <v>4474405392482304</v>
+        <v>709309017096192</v>
       </c>
       <c r="D23" s="1">
-        <v>0.99955165386199951</v>
+        <v>0.99977582693099976</v>
       </c>
       <c r="E23" s="2">
-        <v>2057672320</v>
+        <v>709308928</v>
       </c>
       <c r="F23" s="1">
-        <v>13023777</v>
+        <v>7345124.5</v>
       </c>
       <c r="G23" s="1">
-        <v>0.029867907986044884</v>
+        <v>0.17485350370407104</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1">
-        <v>35465232</v>
-      </c>
-      <c r="B24" s="2">
-        <v>3287503872</v>
-      </c>
-      <c r="C24" s="2">
-        <v>6891441993285632</v>
-      </c>
-      <c r="D24" s="1">
-        <v>0.99977582693099976</v>
-      </c>
-      <c r="E24" s="2">
-        <v>6891442176</v>
-      </c>
-      <c r="F24" s="1">
-        <v>13023777</v>
-      </c>
-      <c r="G24" s="1">
-        <v>0.023092702031135559</v>
-      </c>
-      <c r="H24" s="1"/>
-      <c r="I24" t="s">
         <v>10</v>
       </c>
     </row>
@@ -5184,22 +5157,22 @@
         <v>36138868</v>
       </c>
       <c r="B2" s="2">
-        <v>4935397.5</v>
+        <v>4351267</v>
       </c>
       <c r="C2" s="2">
-        <v>130739962118144</v>
+        <v>70452923858944</v>
       </c>
       <c r="D2" s="1">
         <v>0.88004446029663086</v>
       </c>
       <c r="E2" s="2">
-        <v>16240833</v>
+        <v>14955530</v>
       </c>
       <c r="F2" s="1">
-        <v>15685543</v>
+        <v>8453012</v>
       </c>
       <c r="G2" s="1">
-        <v>0.00013586577551905066</v>
+        <v>0.00014747306704521179</v>
       </c>
       <c r="H2" s="1">
         <v>2021</v>
@@ -5213,22 +5186,22 @@
         <v>36138868</v>
       </c>
       <c r="B3" s="2">
-        <v>25185042</v>
+        <v>23045918</v>
       </c>
       <c r="C3" s="2">
-        <v>141113214107648</v>
+        <v>75480803835904</v>
       </c>
       <c r="D3" s="1">
         <v>0.89000928401947021</v>
       </c>
       <c r="E3" s="2">
-        <v>31991970</v>
+        <v>29378328</v>
       </c>
       <c r="F3" s="1">
-        <v>15685543</v>
+        <v>8453012</v>
       </c>
       <c r="G3" s="1">
-        <v>7.6025404268875718e-05</v>
+        <v>8.2311184087302536e-05</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" t="s">
@@ -5240,22 +5213,22 @@
         <v>36138868</v>
       </c>
       <c r="B4" s="2">
-        <v>38263052</v>
+        <v>35066988</v>
       </c>
       <c r="C4" s="2">
-        <v>152129872330752</v>
+        <v>80136732934144</v>
       </c>
       <c r="D4" s="1">
-        <v>0.90009540319442749</v>
+        <v>0.90009844303131104</v>
       </c>
       <c r="E4" s="2">
-        <v>42920756</v>
+        <v>39081112</v>
       </c>
       <c r="F4" s="1">
-        <v>15685543</v>
+        <v>8453012</v>
       </c>
       <c r="G4" s="1">
-        <v>0.00068043777719140053</v>
+        <v>0.00077051552943885326</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" t="s">
@@ -5267,22 +5240,22 @@
         <v>36138868</v>
       </c>
       <c r="B5" s="2">
-        <v>47866152</v>
+        <v>43011824</v>
       </c>
       <c r="C5" s="2">
-        <v>164233710927872</v>
+        <v>84686722301952</v>
       </c>
       <c r="D5" s="1">
-        <v>0.91006326675415039</v>
+        <v>0.9100654125213623</v>
       </c>
       <c r="E5" s="2">
-        <v>51820884</v>
+        <v>45985324</v>
       </c>
       <c r="F5" s="1">
-        <v>15685543</v>
+        <v>8453012</v>
       </c>
       <c r="G5" s="1">
-        <v>0.0012063274625688791</v>
+        <v>0.0013798681320622563</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" t="s">
@@ -5294,22 +5267,22 @@
         <v>36138868</v>
       </c>
       <c r="B6" s="2">
-        <v>55544384</v>
+        <v>49138900</v>
       </c>
       <c r="C6" s="2">
-        <v>178241578991616</v>
+        <v>89528131911680</v>
       </c>
       <c r="D6" s="1">
-        <v>0.92002856731414795</v>
+        <v>0.92006498575210571</v>
       </c>
       <c r="E6" s="2">
-        <v>59399744</v>
+        <v>51849708</v>
       </c>
       <c r="F6" s="1">
-        <v>15685543</v>
+        <v>8453012</v>
       </c>
       <c r="G6" s="1">
-        <v>0.0018889468628913164</v>
+        <v>0.0021992253605276346</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" t="s">
@@ -5321,22 +5294,22 @@
         <v>36138868</v>
       </c>
       <c r="B7" s="2">
-        <v>63508852</v>
+        <v>54575628</v>
       </c>
       <c r="C7" s="2">
-        <v>195399184809984</v>
+        <v>94888410480640</v>
       </c>
       <c r="D7" s="1">
-        <v>0.93011772632598877</v>
+        <v>0.93002057075500488</v>
       </c>
       <c r="E7" s="2">
-        <v>67784424</v>
+        <v>57290152</v>
       </c>
       <c r="F7" s="1">
-        <v>15685543</v>
+        <v>8453012</v>
       </c>
       <c r="G7" s="1">
-        <v>0.0035551323089748621</v>
+        <v>0.0043646045960485935</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" t="s">
@@ -5348,22 +5321,22 @@
         <v>36138868</v>
       </c>
       <c r="B8" s="2">
-        <v>72207856</v>
+        <v>60722664</v>
       </c>
       <c r="C8" s="2">
-        <v>216607951421440</v>
+        <v>101201886576640</v>
       </c>
       <c r="D8" s="1">
-        <v>0.94007664918899536</v>
+        <v>0.94008195400238037</v>
       </c>
       <c r="E8" s="2">
-        <v>77384408</v>
+        <v>63245588</v>
       </c>
       <c r="F8" s="1">
-        <v>15685543</v>
+        <v>8453012</v>
       </c>
       <c r="G8" s="1">
-        <v>0.0076103862375020981</v>
+        <v>0.009185408242046833</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" t="s">
@@ -5375,22 +5348,22 @@
         <v>36138868</v>
       </c>
       <c r="B9" s="2">
-        <v>83148720</v>
+        <v>66303244</v>
       </c>
       <c r="C9" s="2">
-        <v>244402010193920</v>
+        <v>108777101590528</v>
       </c>
       <c r="D9" s="1">
-        <v>0.95004868507385254</v>
+        <v>0.9500507116317749</v>
       </c>
       <c r="E9" s="2">
-        <v>90066040</v>
+        <v>69331880</v>
       </c>
       <c r="F9" s="1">
-        <v>15685543</v>
+        <v>8453012</v>
       </c>
       <c r="G9" s="1">
-        <v>0.012396081350743771</v>
+        <v>0.016154799610376358</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" t="s">
@@ -5402,22 +5375,22 @@
         <v>36138868</v>
       </c>
       <c r="B10" s="2">
-        <v>97820352</v>
+        <v>73033624</v>
       </c>
       <c r="C10" s="2">
-        <v>282867519193088</v>
+        <v>118611754614784</v>
       </c>
       <c r="D10" s="1">
-        <v>0.96001440286636353</v>
+        <v>0.96001893281936646</v>
       </c>
       <c r="E10" s="2">
-        <v>107595440</v>
+        <v>77903248</v>
       </c>
       <c r="F10" s="1">
-        <v>15685543</v>
+        <v>8453012</v>
       </c>
       <c r="G10" s="1">
-        <v>0.016371915116906166</v>
+        <v>0.02313980832695961</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" t="s">
@@ -5429,22 +5402,22 @@
         <v>36138868</v>
       </c>
       <c r="B11" s="2">
-        <v>118845296</v>
+        <v>81217544</v>
       </c>
       <c r="C11" s="2">
-        <v>342014755340288</v>
+        <v>132343285153792</v>
       </c>
       <c r="D11" s="1">
-        <v>0.97010332345962524</v>
+        <v>0.9701034426689148</v>
       </c>
       <c r="E11" s="2">
-        <v>133862576</v>
+        <v>90739824</v>
       </c>
       <c r="F11" s="1">
-        <v>15685543</v>
+        <v>8453012</v>
       </c>
       <c r="G11" s="1">
-        <v>0.022883106023073197</v>
+        <v>0.03265756368637085</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" t="s">
@@ -5456,22 +5429,22 @@
         <v>36138868</v>
       </c>
       <c r="B12" s="2">
-        <v>154266592</v>
+        <v>100985624</v>
       </c>
       <c r="C12" s="2">
-        <v>446091275272192</v>
+        <v>153158181453824</v>
       </c>
       <c r="D12" s="1">
-        <v>0.98006892204284668</v>
+        <v>0.98007315397262573</v>
       </c>
       <c r="E12" s="2">
-        <v>191145344</v>
+        <v>113084248</v>
       </c>
       <c r="F12" s="1">
-        <v>15685543</v>
+        <v>8453012</v>
       </c>
       <c r="G12" s="1">
-        <v>0.03436824306845665</v>
+        <v>0.056777879595756531</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" t="s">
@@ -5483,22 +5456,22 @@
         <v>36138868</v>
       </c>
       <c r="B13" s="2">
-        <v>245859536</v>
+        <v>129360232</v>
       </c>
       <c r="C13" s="2">
-        <v>701035098144768</v>
+        <v>193214824841216</v>
       </c>
       <c r="D13" s="1">
-        <v>0.99003440141677857</v>
+        <v>0.99003446102142334</v>
       </c>
       <c r="E13" s="2">
-        <v>253957424</v>
+        <v>130201616</v>
       </c>
       <c r="F13" s="1">
-        <v>15685543</v>
+        <v>8453012</v>
       </c>
       <c r="G13" s="1">
-        <v>0.038492675870656967</v>
+        <v>0.072738200426101685</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" t="s">
@@ -5510,22 +5483,22 @@
         <v>36138868</v>
       </c>
       <c r="B14" s="2">
-        <v>265281488</v>
+        <v>131234056</v>
       </c>
       <c r="C14" s="2">
-        <v>750033091690496</v>
+        <v>200119353868288</v>
       </c>
       <c r="D14" s="1">
-        <v>0.99101871252059937</v>
+        <v>0.99101853370666504</v>
       </c>
       <c r="E14" s="2">
-        <v>273800608</v>
+        <v>132925736</v>
       </c>
       <c r="F14" s="1">
-        <v>15685543</v>
+        <v>8453012</v>
       </c>
       <c r="G14" s="1">
-        <v>0.037923015654087067</v>
+        <v>0.07502417266368866</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" t="s">
@@ -5537,22 +5510,22 @@
         <v>36138868</v>
       </c>
       <c r="B15" s="2">
-        <v>286163232</v>
+        <v>134672864</v>
       </c>
       <c r="C15" s="2">
-        <v>808646980141056</v>
+        <v>208391108558848</v>
       </c>
       <c r="D15" s="1">
-        <v>0.99200296401977539</v>
+        <v>0.99200302362442017</v>
       </c>
       <c r="E15" s="2">
-        <v>298899264</v>
+        <v>137733248</v>
       </c>
       <c r="F15" s="1">
-        <v>15685543</v>
+        <v>8453012</v>
       </c>
       <c r="G15" s="1">
-        <v>0.038010518997907639</v>
+        <v>0.080911219120025635</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" t="s">
@@ -5564,22 +5537,22 @@
         <v>36138868</v>
       </c>
       <c r="B16" s="2">
-        <v>315611040</v>
+        <v>140330736</v>
       </c>
       <c r="C16" s="2">
-        <v>890571199610880</v>
+        <v>219747270524928</v>
       </c>
       <c r="D16" s="1">
         <v>0.9931102991104126</v>
       </c>
       <c r="E16" s="2">
-        <v>329945888</v>
+        <v>143824320</v>
       </c>
       <c r="F16" s="1">
-        <v>15685543</v>
+        <v>8453012</v>
       </c>
       <c r="G16" s="1">
-        <v>0.039304561913013458</v>
+        <v>0.084159672260284424</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" t="s">
@@ -5591,22 +5564,22 @@
         <v>36138868</v>
       </c>
       <c r="B17" s="2">
-        <v>349642400</v>
+        <v>146659872</v>
       </c>
       <c r="C17" s="2">
-        <v>984000898269184</v>
+        <v>232399724085248</v>
       </c>
       <c r="D17" s="1">
-        <v>0.99409443140029907</v>
+        <v>0.99409449100494385</v>
       </c>
       <c r="E17" s="2">
-        <v>367881728</v>
+        <v>149432512</v>
       </c>
       <c r="F17" s="1">
-        <v>15685543</v>
+        <v>8453012</v>
       </c>
       <c r="G17" s="1">
-        <v>0.03923579677939415</v>
+        <v>0.089875593781471253</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" t="s">
@@ -5618,22 +5591,22 @@
         <v>36138868</v>
       </c>
       <c r="B18" s="2">
-        <v>392086688</v>
+        <v>153626672</v>
       </c>
       <c r="C18" s="2">
-        <v>1107233039450112</v>
+        <v>248992139051008</v>
       </c>
       <c r="D18" s="1">
-        <v>0.99507874250411987</v>
+        <v>0.9950786828994751</v>
       </c>
       <c r="E18" s="2">
-        <v>416910336</v>
+        <v>160260096</v>
       </c>
       <c r="F18" s="1">
-        <v>15685543</v>
+        <v>8453012</v>
       </c>
       <c r="G18" s="1">
-        <v>0.03933330625295639</v>
+        <v>0.095529280602931976</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" t="s">
@@ -5645,22 +5618,22 @@
         <v>36138868</v>
       </c>
       <c r="B19" s="2">
-        <v>452516096</v>
+        <v>164749792</v>
       </c>
       <c r="C19" s="2">
-        <v>1279816099692544</v>
+        <v>271177339633664</v>
       </c>
       <c r="D19" s="1">
         <v>0.9960629940032959</v>
       </c>
       <c r="E19" s="2">
-        <v>484375808</v>
+        <v>175702896</v>
       </c>
       <c r="F19" s="1">
-        <v>15685543</v>
+        <v>8453012</v>
       </c>
       <c r="G19" s="1">
-        <v>0.038623616099357605</v>
+        <v>0.10042359679937363</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" t="s">
@@ -5672,22 +5645,22 @@
         <v>36138868</v>
       </c>
       <c r="B20" s="2">
-        <v>538221568</v>
+        <v>191675760</v>
       </c>
       <c r="C20" s="2">
-        <v>1544957986865152</v>
+        <v>303003936489472</v>
       </c>
       <c r="D20" s="1">
-        <v>0.99704724550247192</v>
+        <v>0.9970473051071167</v>
       </c>
       <c r="E20" s="2">
-        <v>606641664</v>
+        <v>196248272</v>
       </c>
       <c r="F20" s="1">
-        <v>15685543</v>
+        <v>8453012</v>
       </c>
       <c r="G20" s="1">
-        <v>0.040356032550334931</v>
+        <v>0.11489391326904297</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" t="s">
@@ -5699,22 +5672,22 @@
         <v>36138868</v>
       </c>
       <c r="B21" s="2">
-        <v>719354176</v>
+        <v>201580944</v>
       </c>
       <c r="C21" s="2">
-        <v>2014122631757824</v>
+        <v>356379508342784</v>
       </c>
       <c r="D21" s="1">
         <v>0.99803149700164795</v>
       </c>
       <c r="E21" s="2">
-        <v>873432896</v>
+        <v>223990480</v>
       </c>
       <c r="F21" s="1">
-        <v>15685543</v>
+        <v>8453012</v>
       </c>
       <c r="G21" s="1">
-        <v>0.03724316880106926</v>
+        <v>0.13033302128314972</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" t="s">
@@ -5726,22 +5699,22 @@
         <v>36138868</v>
       </c>
       <c r="B22" s="2">
-        <v>1176645120</v>
+        <v>263712976</v>
       </c>
       <c r="C22" s="2">
-        <v>3154844336521216</v>
+        <v>488772311449600</v>
       </c>
       <c r="D22" s="1">
         <v>0.99901574850082397</v>
       </c>
       <c r="E22" s="2">
-        <v>1241170432</v>
+        <v>269872256</v>
       </c>
       <c r="F22" s="1">
-        <v>15685543</v>
+        <v>8453012</v>
       </c>
       <c r="G22" s="1">
-        <v>0.035288237035274506</v>
+        <v>0.1438007801771164</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" t="s">
@@ -5753,22 +5726,22 @@
         <v>36138868</v>
       </c>
       <c r="B23" s="2">
-        <v>1470690944</v>
+        <v>288487296</v>
       </c>
       <c r="C23" s="2">
-        <v>3792711941357568</v>
+        <v>561736256061440</v>
       </c>
       <c r="D23" s="1">
         <v>0.99926179647445679</v>
       </c>
       <c r="E23" s="2">
-        <v>1581007872</v>
+        <v>298437760</v>
       </c>
       <c r="F23" s="1">
-        <v>15685543</v>
+        <v>8453012</v>
       </c>
       <c r="G23" s="1">
-        <v>0.030651843175292015</v>
+        <v>0.14318752288818359</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" t="s">
@@ -5780,22 +5753,22 @@
         <v>36138868</v>
       </c>
       <c r="B24" s="2">
-        <v>2015294848</v>
+        <v>338353376</v>
       </c>
       <c r="C24" s="2">
-        <v>4898688300220416</v>
+        <v>693400324014080</v>
       </c>
       <c r="D24" s="1">
         <v>0.99950790405273438</v>
       </c>
       <c r="E24" s="2">
-        <v>2285117184</v>
+        <v>367268160</v>
       </c>
       <c r="F24" s="1">
-        <v>15685543</v>
+        <v>8453012</v>
       </c>
       <c r="G24" s="1">
-        <v>0.028645800426602364</v>
+        <v>0.15450634062290192</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" t="s">
@@ -5807,22 +5780,22 @@
         <v>36138868</v>
       </c>
       <c r="B25" s="2">
-        <v>3683667968</v>
+        <v>509138208</v>
       </c>
       <c r="C25" s="2">
-        <v>7512259651698688</v>
+        <v>1019532491620352</v>
       </c>
       <c r="D25" s="1">
         <v>0.99975395202636719</v>
       </c>
       <c r="E25" s="2">
-        <v>7512259584</v>
+        <v>1019532480</v>
       </c>
       <c r="F25" s="1">
-        <v>15685543</v>
+        <v>8453012</v>
       </c>
       <c r="G25" s="1">
-        <v>0.021463882178068161</v>
+        <v>0.13827565312385559</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" t="s">
@@ -5872,22 +5845,22 @@
         <v>36806212</v>
       </c>
       <c r="B2" s="2">
-        <v>15938235</v>
+        <v>14813875</v>
       </c>
       <c r="C2" s="2">
-        <v>140674657681408</v>
+        <v>76324555194368</v>
       </c>
       <c r="D2" s="1">
         <v>0.86003190279006958</v>
       </c>
       <c r="E2" s="2">
-        <v>22787872</v>
+        <v>21193254</v>
       </c>
       <c r="F2" s="1">
-        <v>19756396</v>
+        <v>10744372</v>
       </c>
       <c r="G2" s="1">
-        <v>7.207115413621068e-05</v>
+        <v>7.7349301136564463e-05</v>
       </c>
       <c r="H2" s="1">
         <v>2022</v>
@@ -5901,22 +5874,22 @@
         <v>36806212</v>
       </c>
       <c r="B3" s="2">
-        <v>29023178</v>
+        <v>27005174</v>
       </c>
       <c r="C3" s="2">
-        <v>149763949330432</v>
+        <v>80575289360384</v>
       </c>
       <c r="D3" s="1">
         <v>0.87005120515823364</v>
       </c>
       <c r="E3" s="2">
-        <v>33992732</v>
+        <v>31426830</v>
       </c>
       <c r="F3" s="1">
-        <v>19756396</v>
+        <v>10744372</v>
       </c>
       <c r="G3" s="1">
-        <v>5.8275232731830329e-05</v>
+        <v>8.9641005615703762e-05</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" t="s">
@@ -5928,22 +5901,22 @@
         <v>36806212</v>
       </c>
       <c r="B4" s="2">
-        <v>38789988</v>
+        <v>35520224</v>
       </c>
       <c r="C4" s="2">
-        <v>159435527815168</v>
+        <v>84680372125696</v>
       </c>
       <c r="D4" s="1">
-        <v>0.88007020950317383</v>
+        <v>0.88006842136383057</v>
       </c>
       <c r="E4" s="2">
-        <v>42425464</v>
+        <v>39085996</v>
       </c>
       <c r="F4" s="1">
-        <v>19756396</v>
+        <v>10744372</v>
       </c>
       <c r="G4" s="1">
-        <v>0.00037697658990509808</v>
+        <v>0.00041426648385822773</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" t="s">
@@ -5955,22 +5928,22 @@
         <v>36806212</v>
       </c>
       <c r="B5" s="2">
-        <v>46149176</v>
+        <v>41833164</v>
       </c>
       <c r="C5" s="2">
-        <v>170101894545408</v>
+        <v>88853176123392</v>
       </c>
       <c r="D5" s="1">
-        <v>0.89008939266204834</v>
+        <v>0.89012420177459717</v>
       </c>
       <c r="E5" s="2">
-        <v>49889612</v>
+        <v>44808864</v>
       </c>
       <c r="F5" s="1">
-        <v>19756396</v>
+        <v>10744372</v>
       </c>
       <c r="G5" s="1">
-        <v>0.0010147312423214316</v>
+        <v>0.0011439332738518715</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" t="s">
@@ -5982,22 +5955,22 @@
         <v>36806212</v>
       </c>
       <c r="B6" s="2">
-        <v>53553192</v>
+        <v>47110748</v>
       </c>
       <c r="C6" s="2">
-        <v>182157565755392</v>
+        <v>93234151817216</v>
       </c>
       <c r="D6" s="1">
-        <v>0.90010726451873779</v>
+        <v>0.90006458759307861</v>
       </c>
       <c r="E6" s="2">
-        <v>56486180</v>
+        <v>49394028</v>
       </c>
       <c r="F6" s="1">
-        <v>19756396</v>
+        <v>10744372</v>
       </c>
       <c r="G6" s="1">
-        <v>0.0011960177216678858</v>
+        <v>0.0013759370194748044</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" t="s">
@@ -6009,22 +5982,22 @@
         <v>36806212</v>
       </c>
       <c r="B7" s="2">
-        <v>59691464</v>
+        <v>51955196</v>
       </c>
       <c r="C7" s="2">
-        <v>196168789262336</v>
+        <v>98083748708352</v>
       </c>
       <c r="D7" s="1">
-        <v>0.91012728214263916</v>
+        <v>0.91001832485198975</v>
       </c>
       <c r="E7" s="2">
-        <v>62965812</v>
+        <v>53871124</v>
       </c>
       <c r="F7" s="1">
-        <v>19756396</v>
+        <v>10744372</v>
       </c>
       <c r="G7" s="1">
-        <v>0.0019257473759353161</v>
+        <v>0.0023033355828374624</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" t="s">
@@ -6036,22 +6009,22 @@
         <v>36806212</v>
       </c>
       <c r="B8" s="2">
-        <v>66549576</v>
+        <v>56234436</v>
       </c>
       <c r="C8" s="2">
-        <v>212880238575616</v>
+        <v>103625422536704</v>
       </c>
       <c r="D8" s="1">
-        <v>0.92014569044113159</v>
+        <v>0.9200405478477478</v>
       </c>
       <c r="E8" s="2">
-        <v>70322600</v>
+        <v>58345656</v>
       </c>
       <c r="F8" s="1">
-        <v>19756396</v>
+        <v>10744372</v>
       </c>
       <c r="G8" s="1">
-        <v>0.0032909484580159187</v>
+        <v>0.0042168120853602886</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" t="s">
@@ -6063,22 +6036,22 @@
         <v>36806212</v>
       </c>
       <c r="B9" s="2">
-        <v>74428344</v>
+        <v>60510612</v>
       </c>
       <c r="C9" s="2">
-        <v>232983587979264</v>
+        <v>110079105826816</v>
       </c>
       <c r="D9" s="1">
-        <v>0.93001490831375122</v>
+        <v>0.93001538515090942</v>
       </c>
       <c r="E9" s="2">
-        <v>78872944</v>
+        <v>63429660</v>
       </c>
       <c r="F9" s="1">
-        <v>19756396</v>
+        <v>10744372</v>
       </c>
       <c r="G9" s="1">
-        <v>0.0062387916259467602</v>
+        <v>0.0076444661244750023</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" t="s">
@@ -6090,22 +6063,22 @@
         <v>36806212</v>
       </c>
       <c r="B10" s="2">
-        <v>83808176</v>
+        <v>65701148</v>
       </c>
       <c r="C10" s="2">
-        <v>258735524020224</v>
+        <v>117874244976640</v>
       </c>
       <c r="D10" s="1">
-        <v>0.94003504514694214</v>
+        <v>0.94003552198410034</v>
       </c>
       <c r="E10" s="2">
-        <v>89398312</v>
+        <v>68477736</v>
       </c>
       <c r="F10" s="1">
-        <v>19756396</v>
+        <v>10744372</v>
       </c>
       <c r="G10" s="1">
-        <v>0.010250932537019253</v>
+        <v>0.013285047374665737</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" t="s">
@@ -6117,22 +6090,22 @@
         <v>36806212</v>
       </c>
       <c r="B11" s="2">
-        <v>95859896</v>
+        <v>71080976</v>
       </c>
       <c r="C11" s="2">
-        <v>292702121885696</v>
+        <v>127793698439168</v>
       </c>
       <c r="D11" s="1">
-        <v>0.95005357265472412</v>
+        <v>0.95006340742111206</v>
       </c>
       <c r="E11" s="2">
-        <v>103504936</v>
+        <v>75496672</v>
       </c>
       <c r="F11" s="1">
-        <v>19756396</v>
+        <v>10744372</v>
       </c>
       <c r="G11" s="1">
-        <v>0.014463942497968674</v>
+        <v>0.020183200016617775</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" t="s">
@@ -6144,22 +6117,22 @@
         <v>36806212</v>
       </c>
       <c r="B12" s="2">
-        <v>112464360</v>
+        <v>79810552</v>
       </c>
       <c r="C12" s="2">
-        <v>340181743828992</v>
+        <v>140942220722176</v>
       </c>
       <c r="D12" s="1">
-        <v>0.96007329225540161</v>
+        <v>0.96009606122970581</v>
       </c>
       <c r="E12" s="2">
-        <v>122705216</v>
+        <v>83905608</v>
       </c>
       <c r="F12" s="1">
-        <v>19756396</v>
+        <v>10744372</v>
       </c>
       <c r="G12" s="1">
-        <v>0.017344845458865166</v>
+        <v>0.024707911536097527</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" t="s">
@@ -6171,22 +6144,22 @@
         <v>36806212</v>
       </c>
       <c r="B13" s="2">
-        <v>134190768</v>
+        <v>90797504</v>
       </c>
       <c r="C13" s="2">
-        <v>413035160141824</v>
+        <v>160010516561920</v>
       </c>
       <c r="D13" s="1">
-        <v>0.97009223699569702</v>
+        <v>0.97009408473968506</v>
       </c>
       <c r="E13" s="2">
-        <v>153030640</v>
+        <v>100317520</v>
       </c>
       <c r="F13" s="1">
-        <v>19756396</v>
+        <v>10744372</v>
       </c>
       <c r="G13" s="1">
-        <v>0.025833776220679283</v>
+        <v>0.038939163088798523</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" t="s">
@@ -6198,22 +6171,22 @@
         <v>36806212</v>
       </c>
       <c r="B14" s="2">
-        <v>177435824</v>
+        <v>110131216</v>
       </c>
       <c r="C14" s="2">
-        <v>544016496066560</v>
+        <v>190075992276992</v>
       </c>
       <c r="D14" s="1">
-        <v>0.98011142015457153</v>
+        <v>0.98011136054992676</v>
       </c>
       <c r="E14" s="2">
-        <v>219795712</v>
+        <v>124840888</v>
       </c>
       <c r="F14" s="1">
-        <v>19756396</v>
+        <v>10744372</v>
       </c>
       <c r="G14" s="1">
-        <v>0.036253690719604492</v>
+        <v>0.062019139528274536</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" t="s">
@@ -6225,22 +6198,22 @@
         <v>36806212</v>
       </c>
       <c r="B15" s="2">
-        <v>285347008</v>
+        <v>141355984</v>
       </c>
       <c r="C15" s="2">
-        <v>873148866101248</v>
+        <v>256300764102656</v>
       </c>
       <c r="D15" s="1">
-        <v>0.9901304841041565</v>
+        <v>0.99013054370880127</v>
       </c>
       <c r="E15" s="2">
-        <v>292973632</v>
+        <v>142836128</v>
       </c>
       <c r="F15" s="1">
-        <v>19756396</v>
+        <v>10744372</v>
       </c>
       <c r="G15" s="1">
-        <v>0.038716547191143036</v>
+        <v>0.076017163693904877</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" t="s">
@@ -6252,22 +6225,22 @@
         <v>36806212</v>
       </c>
       <c r="B16" s="2">
-        <v>304512512</v>
+        <v>144549184</v>
       </c>
       <c r="C16" s="2">
-        <v>931169042432000</v>
+        <v>267646339645440</v>
       </c>
       <c r="D16" s="1">
         <v>0.99102771282196045</v>
       </c>
       <c r="E16" s="2">
-        <v>315547616</v>
+        <v>147109680</v>
       </c>
       <c r="F16" s="1">
-        <v>19756396</v>
+        <v>10744372</v>
       </c>
       <c r="G16" s="1">
-        <v>0.039233576506376267</v>
+        <v>0.081427685916423798</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" t="s">
@@ -6279,22 +6252,22 @@
         <v>36806212</v>
       </c>
       <c r="B17" s="2">
-        <v>331714432</v>
+        <v>150488848</v>
       </c>
       <c r="C17" s="2">
-        <v>1012474182631424</v>
+        <v>283566491566080</v>
       </c>
       <c r="D17" s="1">
         <v>0.99207448959350586</v>
       </c>
       <c r="E17" s="2">
-        <v>344892896</v>
+        <v>152510272</v>
       </c>
       <c r="F17" s="1">
-        <v>19756396</v>
+        <v>10744372</v>
       </c>
       <c r="G17" s="1">
-        <v>0.039439283311367035</v>
+        <v>0.085660763084888458</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" t="s">
@@ -6306,22 +6279,22 @@
         <v>36806212</v>
       </c>
       <c r="B18" s="2">
-        <v>364423392</v>
+        <v>154434448</v>
       </c>
       <c r="C18" s="2">
-        <v>1114066802180096</v>
+        <v>303510138650624</v>
       </c>
       <c r="D18" s="1">
         <v>0.99312126636505127</v>
       </c>
       <c r="E18" s="2">
-        <v>378566432</v>
+        <v>155904336</v>
       </c>
       <c r="F18" s="1">
-        <v>19756396</v>
+        <v>10744372</v>
       </c>
       <c r="G18" s="1">
-        <v>0.038916315883398056</v>
+        <v>0.087111234664916992</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" t="s">
@@ -6333,22 +6306,22 @@
         <v>36806212</v>
       </c>
       <c r="B19" s="2">
-        <v>400059136</v>
+        <v>158895056</v>
       </c>
       <c r="C19" s="2">
-        <v>1224389949390848</v>
+        <v>325650661507072</v>
       </c>
       <c r="D19" s="1">
         <v>0.99401849508285522</v>
       </c>
       <c r="E19" s="2">
-        <v>421161024</v>
+        <v>163223808</v>
       </c>
       <c r="F19" s="1">
-        <v>19756396</v>
+        <v>10744372</v>
       </c>
       <c r="G19" s="1">
-        <v>0.038815770298242569</v>
+        <v>0.091620862483978271</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" t="s">
@@ -6360,22 +6333,22 @@
         <v>36806212</v>
       </c>
       <c r="B20" s="2">
-        <v>451968448</v>
+        <v>174230976</v>
       </c>
       <c r="C20" s="2">
-        <v>1394769422974976</v>
+        <v>360106466213888</v>
       </c>
       <c r="D20" s="1">
-        <v>0.99506521224975586</v>
+        <v>0.99506527185440064</v>
       </c>
       <c r="E20" s="2">
-        <v>478992992</v>
+        <v>181896336</v>
       </c>
       <c r="F20" s="1">
-        <v>19756396</v>
+        <v>10744372</v>
       </c>
       <c r="G20" s="1">
-        <v>0.037553787231445313</v>
+        <v>0.095935538411140442</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" t="s">
@@ -6387,22 +6360,22 @@
         <v>36806212</v>
       </c>
       <c r="B21" s="2">
-        <v>522147776</v>
+        <v>203415584</v>
       </c>
       <c r="C21" s="2">
-        <v>1641328194617344</v>
+        <v>408084304363520</v>
       </c>
       <c r="D21" s="1">
         <v>0.99611198902130127</v>
       </c>
       <c r="E21" s="2">
-        <v>564570816</v>
+        <v>207845680</v>
       </c>
       <c r="F21" s="1">
-        <v>19756396</v>
+        <v>10744372</v>
       </c>
       <c r="G21" s="1">
-        <v>0.042729936540126801</v>
+        <v>0.10814506560564041</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" t="s">
@@ -6414,22 +6387,22 @@
         <v>36806212</v>
       </c>
       <c r="B22" s="2">
-        <v>634862272</v>
+        <v>216974816</v>
       </c>
       <c r="C22" s="2">
-        <v>1964361140666368</v>
+        <v>468157005299712</v>
       </c>
       <c r="D22" s="1">
         <v>0.99700927734375</v>
       </c>
       <c r="E22" s="2">
-        <v>723601856</v>
+        <v>226908848</v>
       </c>
       <c r="F22" s="1">
-        <v>19756396</v>
+        <v>10744372</v>
       </c>
       <c r="G22" s="1">
-        <v>0.04088427871465683</v>
+        <v>0.11928960680961609</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" t="s">
@@ -6441,22 +6414,22 @@
         <v>36806212</v>
       </c>
       <c r="B23" s="2">
-        <v>877163264</v>
+        <v>250005520</v>
       </c>
       <c r="C23" s="2">
-        <v>2632454175195136</v>
+        <v>598058291167232</v>
       </c>
       <c r="D23" s="1">
         <v>0.99805599451065063</v>
       </c>
       <c r="E23" s="2">
-        <v>1103193856</v>
+        <v>287392896</v>
       </c>
       <c r="F23" s="1">
-        <v>19756396</v>
+        <v>10744372</v>
       </c>
       <c r="G23" s="1">
-        <v>0.037903748452663422</v>
+        <v>0.13050152361392975</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" t="s">
@@ -6468,22 +6441,22 @@
         <v>36806212</v>
       </c>
       <c r="B24" s="2">
-        <v>1597053184</v>
+        <v>370578976</v>
       </c>
       <c r="C24" s="2">
-        <v>4416645598543872</v>
+        <v>960512191889408</v>
       </c>
       <c r="D24" s="1">
         <v>0.99910277128219605</v>
       </c>
       <c r="E24" s="2">
-        <v>1726397952</v>
+        <v>388115104</v>
       </c>
       <c r="F24" s="1">
-        <v>19756396</v>
+        <v>10744372</v>
       </c>
       <c r="G24" s="1">
-        <v>0.033393625169992447</v>
+        <v>0.13295415043830872</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" t="s">
@@ -6495,22 +6468,22 @@
         <v>36806212</v>
       </c>
       <c r="B25" s="2">
-        <v>2229728000</v>
+        <v>464064192</v>
       </c>
       <c r="C25" s="2">
-        <v>5761830160957440</v>
+        <v>1246723779330048</v>
       </c>
       <c r="D25" s="1">
         <v>0.99940186738967896</v>
       </c>
       <c r="E25" s="2">
-        <v>2539050240</v>
+        <v>510432992</v>
       </c>
       <c r="F25" s="1">
-        <v>19756396</v>
+        <v>10744372</v>
       </c>
       <c r="G25" s="1">
-        <v>0.03071993961930275</v>
+        <v>0.13566496968269348</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" t="s">
@@ -6522,22 +6495,22 @@
         <v>36806212</v>
       </c>
       <c r="B26" s="2">
-        <v>4093905664</v>
+        <v>774029120</v>
       </c>
       <c r="C26" s="2">
-        <v>8984903542636544</v>
+        <v>1983081426714624</v>
       </c>
       <c r="D26" s="1">
         <v>0.99970096349716187</v>
       </c>
       <c r="E26" s="2">
-        <v>8984903680</v>
+        <v>1983081472</v>
       </c>
       <c r="F26" s="1">
-        <v>19756396</v>
+        <v>10744372</v>
       </c>
       <c r="G26" s="1">
-        <v>0.024515798315405846</v>
+        <v>0.10874081403017044</v>
       </c>
       <c r="H26" s="1"/>
       <c r="I26" t="s">
